--- a/public/FEES REGISTER 20251.xlsx
+++ b/public/FEES REGISTER 20251.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fau\Desktop\Websites\detema_sec\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783A1666-A14A-44ED-9FCC-B60F8D65A8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E90B96-DFFC-4804-A0C7-AA5EF08DBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form 1 East" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1032">
   <si>
     <t>FORM 1 EAST FEES REGISTER</t>
   </si>
@@ -66,27 +64,18 @@
     <t>DUBE AMANDA D</t>
   </si>
   <si>
-    <t>2025/01</t>
-  </si>
-  <si>
     <t>0786863982</t>
   </si>
   <si>
     <t>GARAI RUVIMBO</t>
   </si>
   <si>
-    <t>2025/02</t>
-  </si>
-  <si>
     <t>0778783682</t>
   </si>
   <si>
     <t>KUDZIKIDA PRETTY</t>
   </si>
   <si>
-    <t>2025/03</t>
-  </si>
-  <si>
     <t>0777217239</t>
   </si>
   <si>
@@ -96,45 +85,30 @@
     <t>MHLOPHE NATASHA</t>
   </si>
   <si>
-    <t>2025/04</t>
-  </si>
-  <si>
     <t>0771639849</t>
   </si>
   <si>
     <t>MKOBOTSHO ESNATH</t>
   </si>
   <si>
-    <t>2025/05</t>
-  </si>
-  <si>
     <t>0774386655</t>
   </si>
   <si>
     <t>MOYO BETINA</t>
   </si>
   <si>
-    <t>2025/06</t>
-  </si>
-  <si>
     <t>0777555267</t>
   </si>
   <si>
     <t>MOYO MITCHELL</t>
   </si>
   <si>
-    <t>2025/07</t>
-  </si>
-  <si>
     <t>0776313595</t>
   </si>
   <si>
     <t>MOYO SHANTEL Z</t>
   </si>
   <si>
-    <t>2025/08</t>
-  </si>
-  <si>
     <t>0778108122</t>
   </si>
   <si>
@@ -144,36 +118,24 @@
     <t>MPALA LETHOKUHLE</t>
   </si>
   <si>
-    <t>2025/09</t>
-  </si>
-  <si>
     <t>0713361080</t>
   </si>
   <si>
     <t>MUMPANDE PRISCILLA</t>
   </si>
   <si>
-    <t>2025/10</t>
-  </si>
-  <si>
     <t>0775437932</t>
   </si>
   <si>
     <t xml:space="preserve">NCUBE NOLANGA </t>
   </si>
   <si>
-    <t>2025/11</t>
-  </si>
-  <si>
     <t>0782023477</t>
   </si>
   <si>
     <t>NCUBE SANDILE</t>
   </si>
   <si>
-    <t>2025/12</t>
-  </si>
-  <si>
     <t>0777023758</t>
   </si>
   <si>
@@ -183,231 +145,153 @@
     <t>NYATHI NOMTHANDAZO P</t>
   </si>
   <si>
-    <t>2025/13</t>
-  </si>
-  <si>
     <t>0782535610</t>
   </si>
   <si>
     <t>SAYI REBECCA</t>
   </si>
   <si>
-    <t>2025/14</t>
-  </si>
-  <si>
     <t>0785378917</t>
   </si>
   <si>
     <t>SIBANDA NONHLANHLA S</t>
   </si>
   <si>
-    <t>2025/15</t>
-  </si>
-  <si>
     <t>0785378905</t>
   </si>
   <si>
     <t>SIBANDA REJOICE</t>
   </si>
   <si>
-    <t>2025/16</t>
-  </si>
-  <si>
     <t>0784597373</t>
   </si>
   <si>
     <t>TSHUMA NQOBILE</t>
   </si>
   <si>
-    <t>2025/17</t>
-  </si>
-  <si>
     <t>0779312045</t>
   </si>
   <si>
     <t>ZULU RACHEAL</t>
   </si>
   <si>
-    <t>2025/18</t>
-  </si>
-  <si>
     <t>0773140785</t>
   </si>
   <si>
     <t>MAKANDE BLESSED R</t>
   </si>
   <si>
-    <t>2025/19</t>
-  </si>
-  <si>
     <t>TRANSFARED</t>
   </si>
   <si>
     <t>NDLOVU BEVERLY O</t>
   </si>
   <si>
-    <t>2025/20</t>
-  </si>
-  <si>
     <t>0773430653</t>
   </si>
   <si>
     <t>NCUBE VIMBAI</t>
   </si>
   <si>
-    <t>2025/21</t>
-  </si>
-  <si>
     <t>0779346223</t>
   </si>
   <si>
     <t>NKALA MANASE</t>
   </si>
   <si>
-    <t>2025/22</t>
-  </si>
-  <si>
     <t>0771423340</t>
   </si>
   <si>
     <t>DLADLA THABISO</t>
   </si>
   <si>
-    <t>2025/23</t>
-  </si>
-  <si>
     <t>DZITIRO LEE A</t>
   </si>
   <si>
-    <t>2025/24</t>
-  </si>
-  <si>
     <t>0777085496</t>
   </si>
   <si>
     <t>KUTADZA DELIGHT K</t>
   </si>
   <si>
-    <t>2025/25</t>
-  </si>
-  <si>
     <t>0785516956</t>
   </si>
   <si>
     <t>MKHIZA JUNIOR</t>
   </si>
   <si>
-    <t>2025/26</t>
-  </si>
-  <si>
     <t>0784422305</t>
   </si>
   <si>
     <t>MOYO LOUIS L</t>
   </si>
   <si>
-    <t>2025/27</t>
-  </si>
-  <si>
     <t>07751066092</t>
   </si>
   <si>
     <t>MSIPHA ETERNAL S</t>
   </si>
   <si>
-    <t>2025/28</t>
-  </si>
-  <si>
     <t>0785800378</t>
   </si>
   <si>
     <t>MWEMBE JOHANE</t>
   </si>
   <si>
-    <t>2025/29</t>
-  </si>
-  <si>
     <t>0782865863</t>
   </si>
   <si>
     <t>NCUBE ANDILE A</t>
   </si>
   <si>
-    <t>2025/30</t>
-  </si>
-  <si>
     <t>0775641916</t>
   </si>
   <si>
     <t>NCUBE ANTONY</t>
   </si>
   <si>
-    <t>2025/31</t>
-  </si>
-  <si>
     <t>0777589419</t>
   </si>
   <si>
     <t>NCUBE TADIWANASHE B</t>
   </si>
   <si>
-    <t>2025/32</t>
-  </si>
-  <si>
     <t>0773535421</t>
   </si>
   <si>
     <t>NCUBE TAKUNDA</t>
   </si>
   <si>
-    <t>2025/33</t>
-  </si>
-  <si>
     <t>0783129052</t>
   </si>
   <si>
     <t>NDLOVU DENNIS S</t>
   </si>
   <si>
-    <t>2025/34</t>
-  </si>
-  <si>
     <t>0785361901</t>
   </si>
   <si>
     <t>NYATHI DIVINE</t>
   </si>
   <si>
-    <t>2025/35</t>
-  </si>
-  <si>
     <t>0775905141</t>
   </si>
   <si>
     <t>SIAMATANGA SURMISE P</t>
   </si>
   <si>
-    <t>2025/36</t>
-  </si>
-  <si>
     <t>0775168263</t>
   </si>
   <si>
     <t>SIBANDA EBENEEZAR</t>
   </si>
   <si>
-    <t>2025/37</t>
-  </si>
-  <si>
     <t>0783357835</t>
   </si>
   <si>
     <t>SIBANDA METHEMBE</t>
   </si>
   <si>
-    <t>2025/38</t>
-  </si>
-  <si>
     <t>0777315151</t>
   </si>
   <si>
@@ -417,39 +301,24 @@
     <t>SIBANDA MPENDULO</t>
   </si>
   <si>
-    <t>2025/39</t>
-  </si>
-  <si>
     <t>SIBANDA MTHULISI</t>
   </si>
   <si>
-    <t>2025/40</t>
-  </si>
-  <si>
     <t>SIBANDA WITNESS</t>
   </si>
   <si>
-    <t>2025/41</t>
-  </si>
-  <si>
     <t>0778893534</t>
   </si>
   <si>
     <t>SIBINDI WISEMAN</t>
   </si>
   <si>
-    <t>2025/42</t>
-  </si>
-  <si>
     <t>0782009901</t>
   </si>
   <si>
     <t>SHOKO POSENT</t>
   </si>
   <si>
-    <t>2025/43</t>
-  </si>
-  <si>
     <t>transfered 210</t>
   </si>
   <si>
@@ -459,45 +328,30 @@
     <t>BANDA THANDOLENKOSI</t>
   </si>
   <si>
-    <t>2025/44</t>
-  </si>
-  <si>
     <t>0771674054</t>
   </si>
   <si>
     <t>FOX CYNTHIA</t>
   </si>
   <si>
-    <t>2025/45</t>
-  </si>
-  <si>
     <t>0782003908</t>
   </si>
   <si>
     <t>MASUKU SANDRA</t>
   </si>
   <si>
-    <t>2025/46</t>
-  </si>
-  <si>
     <t>0784110737</t>
   </si>
   <si>
     <t xml:space="preserve">MATHE LINDOKUHLE </t>
   </si>
   <si>
-    <t>2025/47</t>
-  </si>
-  <si>
     <t>0772509876</t>
   </si>
   <si>
     <t>MOYO SANDILE</t>
   </si>
   <si>
-    <t>2025/48</t>
-  </si>
-  <si>
     <t>0776544909</t>
   </si>
   <si>
@@ -507,36 +361,24 @@
     <t>MSIPHA EMELIA F</t>
   </si>
   <si>
-    <t>2025/49</t>
-  </si>
-  <si>
     <t>SOLON                        0</t>
   </si>
   <si>
     <t>MULEYA PRESENCE</t>
   </si>
   <si>
-    <t>2025/50</t>
-  </si>
-  <si>
     <t>0782158285</t>
   </si>
   <si>
     <t>MULEYA SENZENI</t>
   </si>
   <si>
-    <t>2025/51</t>
-  </si>
-  <si>
     <t>0778905957</t>
   </si>
   <si>
     <t>NCUBE THANDEKA L</t>
   </si>
   <si>
-    <t>2025/52</t>
-  </si>
-  <si>
     <t>0785398436</t>
   </si>
   <si>
@@ -546,42 +388,27 @@
     <t>NDEBELE BLESSING T</t>
   </si>
   <si>
-    <t>2025/53</t>
-  </si>
-  <si>
     <t>0783633457</t>
   </si>
   <si>
     <t>NDLOVU NESISA</t>
   </si>
   <si>
-    <t>2025/54</t>
-  </si>
-  <si>
     <t>0784202694</t>
   </si>
   <si>
     <t>NDLOVU PRINCESS</t>
   </si>
   <si>
-    <t>2025/55</t>
-  </si>
-  <si>
     <t>0774386593</t>
   </si>
   <si>
     <t>NDLOVU THEMBELIHLE</t>
   </si>
   <si>
-    <t>2025/56</t>
-  </si>
-  <si>
     <t>NGOZO CIARA G</t>
   </si>
   <si>
-    <t>2025/57</t>
-  </si>
-  <si>
     <t>0778121895</t>
   </si>
   <si>
@@ -591,87 +418,57 @@
     <t>PHIRI NATASHA N</t>
   </si>
   <si>
-    <t>2025/58</t>
-  </si>
-  <si>
     <t>0782163331</t>
   </si>
   <si>
     <t>SHOKO SAMANTHA</t>
   </si>
   <si>
-    <t>2025/59</t>
-  </si>
-  <si>
     <t>0787865583</t>
   </si>
   <si>
     <t>SIBANDA NOXOLO N</t>
   </si>
   <si>
-    <t>2025/60</t>
-  </si>
-  <si>
     <t>0777555374</t>
   </si>
   <si>
     <t>SIBANDA NOZINHLE</t>
   </si>
   <si>
-    <t>2025/61</t>
-  </si>
-  <si>
     <t>SIBANDA PRINCESS</t>
   </si>
   <si>
-    <t>2025/62</t>
-  </si>
-  <si>
     <t>0775434121</t>
   </si>
   <si>
     <t xml:space="preserve">SIBANDA VUYISILE </t>
   </si>
   <si>
-    <t>2025/63</t>
-  </si>
-  <si>
     <t>0785374259</t>
   </si>
   <si>
     <t>NDIMANDE PAMELA</t>
   </si>
   <si>
-    <t>2025/64</t>
-  </si>
-  <si>
     <t>0784087488</t>
   </si>
   <si>
     <t>BIRA TINASHE</t>
   </si>
   <si>
-    <t>2025/65</t>
-  </si>
-  <si>
     <t>0779013948</t>
   </si>
   <si>
     <t>DUBE SILENT</t>
   </si>
   <si>
-    <t>2025/66</t>
-  </si>
-  <si>
     <t>0784235976</t>
   </si>
   <si>
     <t>LUPHAHLA NKOSANA</t>
   </si>
   <si>
-    <t>2025/67</t>
-  </si>
-  <si>
     <t>0780271934</t>
   </si>
   <si>
@@ -681,348 +478,231 @@
     <t>MAGADZIRE DENZEL</t>
   </si>
   <si>
-    <t>2025/68</t>
-  </si>
-  <si>
     <t>0774833389</t>
   </si>
   <si>
     <t>MOYO KWAZINKOSI</t>
   </si>
   <si>
-    <t>2025/69</t>
-  </si>
-  <si>
     <t>0784090053</t>
   </si>
   <si>
     <t>MOYO MELULEKI</t>
   </si>
   <si>
-    <t>2025/70</t>
-  </si>
-  <si>
     <t>0713089654</t>
   </si>
   <si>
     <t>MOYO PRAISE P</t>
   </si>
   <si>
-    <t>2025/71</t>
-  </si>
-  <si>
     <t>0784300955</t>
   </si>
   <si>
     <t>MPALA MDUMISI</t>
   </si>
   <si>
-    <t>2025/72</t>
-  </si>
-  <si>
     <t>0773361080</t>
   </si>
   <si>
     <t>MPOFU ALBERT Z</t>
   </si>
   <si>
-    <t>2025/73</t>
-  </si>
-  <si>
     <t>0786111917</t>
   </si>
   <si>
     <t>MUNENGE LYRON</t>
   </si>
   <si>
-    <t>2025/74</t>
-  </si>
-  <si>
     <t>0772456449</t>
   </si>
   <si>
     <t>MUNKOMBWE JUSTICE</t>
   </si>
   <si>
-    <t>2025/75</t>
-  </si>
-  <si>
     <t>0785651933</t>
   </si>
   <si>
     <t>MUSEVA RICHMAN</t>
   </si>
   <si>
-    <t>2025/76</t>
-  </si>
-  <si>
     <t>0777773609</t>
   </si>
   <si>
     <t>NCUBE SONNY</t>
   </si>
   <si>
-    <t>2025/77</t>
-  </si>
-  <si>
     <t>0784810172</t>
   </si>
   <si>
     <t>NDEBELE MBONGENI</t>
   </si>
   <si>
-    <t>2025/78</t>
-  </si>
-  <si>
     <t>0782165073</t>
   </si>
   <si>
     <t>NDEBELE PRINCE</t>
   </si>
   <si>
-    <t>2025/79</t>
-  </si>
-  <si>
     <t>SOLON                       0</t>
   </si>
   <si>
     <t>NDIMANDE USHER</t>
   </si>
   <si>
-    <t>2025/80</t>
-  </si>
-  <si>
     <t>0782236090</t>
   </si>
   <si>
     <t>NDLOVU MDUDUZI Z</t>
   </si>
   <si>
-    <t>2025/81</t>
-  </si>
-  <si>
     <t>0779024757</t>
   </si>
   <si>
     <t>NDLOVU THANDAZANI</t>
   </si>
   <si>
-    <t>2025/82</t>
-  </si>
-  <si>
     <t>0783416564</t>
   </si>
   <si>
     <t>NGWENYA MICHEAL</t>
   </si>
   <si>
-    <t>2025/83</t>
-  </si>
-  <si>
     <t>0778035855</t>
   </si>
   <si>
     <t>PHIRI PERSEVERANCE</t>
   </si>
   <si>
-    <t>2025/84</t>
-  </si>
-  <si>
     <t>0774006238</t>
   </si>
   <si>
     <t>SIBELO SIBUSISO D</t>
   </si>
   <si>
-    <t>2025/85</t>
-  </si>
-  <si>
     <t>0776530657</t>
   </si>
   <si>
     <t>NGWERUME BERVEN</t>
   </si>
   <si>
-    <t>2025/86</t>
-  </si>
-  <si>
     <t>0774774018</t>
   </si>
   <si>
     <t>SIBANDA BRIAN</t>
   </si>
   <si>
-    <t>2025/87</t>
-  </si>
-  <si>
     <t>FORM 2 EAST FEES REGISTER</t>
   </si>
   <si>
     <t>DLAMIN ALICIA N</t>
   </si>
   <si>
-    <t>2024/01</t>
-  </si>
-  <si>
     <t>0777403956</t>
   </si>
   <si>
     <t>DUBE NOKUTHULA</t>
   </si>
   <si>
-    <t>2024/02</t>
-  </si>
-  <si>
     <t>0785651949</t>
   </si>
   <si>
     <t>DUBE SHALLON</t>
   </si>
   <si>
-    <t>2024/03</t>
-  </si>
-  <si>
     <t>LUNGA GABRIELLA</t>
   </si>
   <si>
-    <t>2024/04</t>
-  </si>
-  <si>
     <t>0773478086</t>
   </si>
   <si>
     <t>MATENGA TENDAI</t>
   </si>
   <si>
-    <t>2024/05</t>
-  </si>
-  <si>
     <t>0785361615</t>
   </si>
   <si>
     <t>MKHWEBU DORCAS</t>
   </si>
   <si>
-    <t>2024/06</t>
-  </si>
-  <si>
     <t>0786962684</t>
   </si>
   <si>
     <t>MOYO THOBILE</t>
   </si>
   <si>
-    <t>2024/07</t>
-  </si>
-  <si>
     <t>0774007356</t>
   </si>
   <si>
     <t>MPOFU VANESSA</t>
   </si>
   <si>
-    <t>2024/08</t>
-  </si>
-  <si>
     <t>0783451525</t>
   </si>
   <si>
     <t xml:space="preserve">NCUBE VALENTINE </t>
   </si>
   <si>
-    <t>2024/09</t>
-  </si>
-  <si>
     <t>0785595402</t>
   </si>
   <si>
     <t>NCUBE THUBELIHLE</t>
   </si>
   <si>
-    <t>2024/10</t>
-  </si>
-  <si>
     <t>0778108701</t>
   </si>
   <si>
     <t>NCUBE BABONGILE</t>
   </si>
   <si>
-    <t>2024/11</t>
-  </si>
-  <si>
     <t>0786799605</t>
   </si>
   <si>
     <t>NDLOVU NTOMBIYOKUKHANYA</t>
   </si>
   <si>
-    <t>2024/12</t>
-  </si>
-  <si>
     <t>0785392560</t>
   </si>
   <si>
     <t>NDLOVU GUGULETHU</t>
   </si>
   <si>
-    <t>2024/13</t>
-  </si>
-  <si>
     <t>S0LON                        63</t>
   </si>
   <si>
     <t>SIBANDA TRISHA N</t>
   </si>
   <si>
-    <t>2024/14</t>
-  </si>
-  <si>
     <t>0779972450</t>
   </si>
   <si>
     <t>TSHUMA KAYLA L</t>
   </si>
   <si>
-    <t>2024/15</t>
-  </si>
-  <si>
     <t>0785408137</t>
   </si>
   <si>
     <t>TSHUMA SHELDONIA</t>
   </si>
   <si>
-    <t>2024/16</t>
-  </si>
-  <si>
     <t>0782163422</t>
   </si>
   <si>
     <t>KHUMALO ABATSHA</t>
   </si>
   <si>
-    <t>2024/17</t>
-  </si>
-  <si>
     <t>0787429100</t>
   </si>
   <si>
     <t>PHIRI BEVERLY</t>
   </si>
   <si>
-    <t>2024/18</t>
-  </si>
-  <si>
     <t>07791591554</t>
   </si>
   <si>
     <t>NDLOVU NONTOKOZO</t>
   </si>
   <si>
-    <t>2024/19</t>
-  </si>
-  <si>
     <t>0779369279</t>
   </si>
   <si>
@@ -1032,9 +712,6 @@
     <t>NGWENYA PRISCA</t>
   </si>
   <si>
-    <t>2024/20</t>
-  </si>
-  <si>
     <t>0775627367</t>
   </si>
   <si>
@@ -1044,9 +721,6 @@
     <t>MHLANGA FAITH M</t>
   </si>
   <si>
-    <t>2024/</t>
-  </si>
-  <si>
     <t>0779145650</t>
   </si>
   <si>
@@ -1059,36 +733,24 @@
     <t>GUMBO ROYCE</t>
   </si>
   <si>
-    <t>2024/21</t>
-  </si>
-  <si>
     <t>0775630991</t>
   </si>
   <si>
     <t>IDI COURAGE</t>
   </si>
   <si>
-    <t>2024/22</t>
-  </si>
-  <si>
     <t>0773783133</t>
   </si>
   <si>
     <t>MPALA BLESSING</t>
   </si>
   <si>
-    <t>2024/23</t>
-  </si>
-  <si>
     <t>0774417017</t>
   </si>
   <si>
     <t>MDLULI MALVIN</t>
   </si>
   <si>
-    <t>2024/24</t>
-  </si>
-  <si>
     <t>0779960750</t>
   </si>
   <si>
@@ -1098,93 +760,60 @@
     <t>MUDIMBA TAPELO</t>
   </si>
   <si>
-    <t>2024/25</t>
-  </si>
-  <si>
     <t>0778108175</t>
   </si>
   <si>
     <t>MUMPANDE CHISYO</t>
   </si>
   <si>
-    <t>2024/26</t>
-  </si>
-  <si>
     <t>0785595440</t>
   </si>
   <si>
     <t>NDEBELE SHALOM M</t>
   </si>
   <si>
-    <t>2024/27</t>
-  </si>
-  <si>
     <t>0778643679</t>
   </si>
   <si>
     <t>NGWENYA SAM</t>
   </si>
   <si>
-    <t>2024/28</t>
-  </si>
-  <si>
     <t>0779366081</t>
   </si>
   <si>
     <t>NDLOVU MBONGENI</t>
   </si>
   <si>
-    <t>2024/29</t>
-  </si>
-  <si>
     <t>NKOMO EUGENE</t>
   </si>
   <si>
-    <t>2024/30</t>
-  </si>
-  <si>
     <t>0778675779</t>
   </si>
   <si>
     <t>NKOMO DUMISILE</t>
   </si>
   <si>
-    <t>2024/31</t>
-  </si>
-  <si>
     <t>0782163414</t>
   </si>
   <si>
     <t>NYATHI PRISSLY T</t>
   </si>
   <si>
-    <t>2024/32</t>
-  </si>
-  <si>
     <t>0774773795</t>
   </si>
   <si>
     <t>SIBANDA SIPHO</t>
   </si>
   <si>
-    <t>2024/33</t>
-  </si>
-  <si>
     <t>0775437117</t>
   </si>
   <si>
     <t>SHISHOLA THAMSANQA</t>
   </si>
   <si>
-    <t>2024/34</t>
-  </si>
-  <si>
     <t>NCUBE LINCOLN</t>
   </si>
   <si>
-    <t>2024/35</t>
-  </si>
-  <si>
     <t>0777322604</t>
   </si>
   <si>
@@ -1194,54 +823,36 @@
     <t>JULY BRIGHT</t>
   </si>
   <si>
-    <t>2024/36</t>
-  </si>
-  <si>
     <t>0784994845</t>
   </si>
   <si>
     <t>NDLOVU JOHNSLY</t>
   </si>
   <si>
-    <t>2024/37</t>
-  </si>
-  <si>
     <t>0786794616</t>
   </si>
   <si>
     <t>PHIRI WAYNE</t>
   </si>
   <si>
-    <t>2024/38</t>
-  </si>
-  <si>
     <t>0779710131</t>
   </si>
   <si>
     <t>MUDIMBA DINGULWAZI</t>
   </si>
   <si>
-    <t>2024/39</t>
-  </si>
-  <si>
     <t>0777333968</t>
   </si>
   <si>
     <t>MOYO METHEMBE</t>
   </si>
   <si>
-    <t>2024/40</t>
-  </si>
-  <si>
     <t>0777704947</t>
   </si>
   <si>
     <t>SIBANDA LINDOKUHLE G</t>
   </si>
   <si>
-    <t>2024/41</t>
-  </si>
-  <si>
     <t>078826740</t>
   </si>
   <si>
@@ -1260,141 +871,93 @@
     <t>DUBE BEAUTY S</t>
   </si>
   <si>
-    <t>2024/42</t>
-  </si>
-  <si>
     <t>0783890753</t>
   </si>
   <si>
     <t>DUBE TERRESA</t>
   </si>
   <si>
-    <t>2024/43</t>
-  </si>
-  <si>
     <t>0776530712</t>
   </si>
   <si>
     <t>GOWERO TSITSI M</t>
   </si>
   <si>
-    <t>2024/44</t>
-  </si>
-  <si>
     <t>0775257931</t>
   </si>
   <si>
     <t>GOMBA SIMELWEYINKOSI P</t>
   </si>
   <si>
-    <t>2024/45</t>
-  </si>
-  <si>
     <t>0771322677</t>
   </si>
   <si>
     <t xml:space="preserve">KHUMALO NATASHA </t>
   </si>
   <si>
-    <t>2024/46</t>
-  </si>
-  <si>
     <t>0773887798</t>
   </si>
   <si>
     <t>MLEYA ANNELINE</t>
   </si>
   <si>
-    <t>2024/47</t>
-  </si>
-  <si>
     <t>0776550259</t>
   </si>
   <si>
     <t>MHLANGA BLESSING</t>
   </si>
   <si>
-    <t>2024/48</t>
-  </si>
-  <si>
     <t>0785652042</t>
   </si>
   <si>
     <t>MHLANGA BEYONCE</t>
   </si>
   <si>
-    <t>2024/49</t>
-  </si>
-  <si>
     <t>0777773563</t>
   </si>
   <si>
     <t>MVULA NOMVULA</t>
   </si>
   <si>
-    <t>2024/50</t>
-  </si>
-  <si>
     <t>0782747440</t>
   </si>
   <si>
     <t>MBEWE PEALLAH N</t>
   </si>
   <si>
-    <t>2024/51</t>
-  </si>
-  <si>
     <t>0779154318</t>
   </si>
   <si>
     <t>MUCHEZANA REJOICE</t>
   </si>
   <si>
-    <t>2024/52</t>
-  </si>
-  <si>
     <t>0789683045</t>
   </si>
   <si>
     <t>MATHE PRECIOUS K</t>
   </si>
   <si>
-    <t>2024/53</t>
-  </si>
-  <si>
     <t>0778668407</t>
   </si>
   <si>
     <t>MADAMOMBE MITCHEL R</t>
   </si>
   <si>
-    <t>2024/54</t>
-  </si>
-  <si>
     <t>MUDENDA LIONA</t>
   </si>
   <si>
-    <t>2024/55</t>
-  </si>
-  <si>
     <t>0782009923</t>
   </si>
   <si>
     <t>MPALA SEKAI</t>
   </si>
   <si>
-    <t>2024/56</t>
-  </si>
-  <si>
     <t>0784202191</t>
   </si>
   <si>
     <t>NDLOVU BEKEZELA</t>
   </si>
   <si>
-    <t>2024/57</t>
-  </si>
-  <si>
     <t>0778840315</t>
   </si>
   <si>
@@ -1404,9 +967,6 @@
     <t>NCUBE LANGELIHLE</t>
   </si>
   <si>
-    <t>2024/58</t>
-  </si>
-  <si>
     <t>0785347379</t>
   </si>
   <si>
@@ -1416,9 +976,6 @@
     <t>SIBANDA NOMAGUGU</t>
   </si>
   <si>
-    <t>2024/59</t>
-  </si>
-  <si>
     <t>0777736704</t>
   </si>
   <si>
@@ -1428,72 +985,48 @@
     <t>SIBANDA MONALISA C</t>
   </si>
   <si>
-    <t>2024/60</t>
-  </si>
-  <si>
     <t>0785594775</t>
   </si>
   <si>
     <t>SITHOLE KIMBERLY M</t>
   </si>
   <si>
-    <t>2024/61</t>
-  </si>
-  <si>
     <t>0785516823</t>
   </si>
   <si>
     <t>SIBANDA MATRON</t>
   </si>
   <si>
-    <t>2024/62</t>
-  </si>
-  <si>
     <t>0774987678</t>
   </si>
   <si>
     <t>TSHUMA CIARA B</t>
   </si>
   <si>
-    <t>2024/63</t>
-  </si>
-  <si>
     <t>0784282577</t>
   </si>
   <si>
     <t>SIBANDA PETRONELA</t>
   </si>
   <si>
-    <t>2024/64</t>
-  </si>
-  <si>
     <t>0779324002</t>
   </si>
   <si>
     <t>TSHUMA TRINITY</t>
   </si>
   <si>
-    <t>2024/65</t>
-  </si>
-  <si>
     <t>0788545169</t>
   </si>
   <si>
     <t>NCUBE SITHABILE</t>
   </si>
   <si>
-    <t>2024/66</t>
-  </si>
-  <si>
     <t>0776288238</t>
   </si>
   <si>
     <t>THEBE SINEMPILO S</t>
   </si>
   <si>
-    <t>2024/67</t>
-  </si>
-  <si>
     <t>MOYO MELINDA T</t>
   </si>
   <si>
@@ -1506,9 +1039,6 @@
     <t>DUBE LINCOLN</t>
   </si>
   <si>
-    <t>2024/68</t>
-  </si>
-  <si>
     <t>07726216993</t>
   </si>
   <si>
@@ -1518,150 +1048,96 @@
     <t>GWENJERE BHEKUMUZI</t>
   </si>
   <si>
-    <t>2024/69</t>
-  </si>
-  <si>
     <t>GUMBO ROY B</t>
   </si>
   <si>
-    <t>2024/70</t>
-  </si>
-  <si>
     <t>MATONGO MICHEAL</t>
   </si>
   <si>
-    <t>2024/71</t>
-  </si>
-  <si>
     <t>0775729427</t>
   </si>
   <si>
     <t>MUGANDE SHADRECK J</t>
   </si>
   <si>
-    <t>2024/72</t>
-  </si>
-  <si>
     <t>0777747317</t>
   </si>
   <si>
     <t>MHLANGA TRYMORE</t>
   </si>
   <si>
-    <t>2024/73</t>
-  </si>
-  <si>
     <t>MOYO BRIAN</t>
   </si>
   <si>
-    <t>2024/74</t>
-  </si>
-  <si>
     <t>0788860015</t>
   </si>
   <si>
     <t>MHLANGA CALVIN</t>
   </si>
   <si>
-    <t>2024/75</t>
-  </si>
-  <si>
     <t>0787709112</t>
   </si>
   <si>
     <t>NYONI BRAIN</t>
   </si>
   <si>
-    <t>2024/76</t>
-  </si>
-  <si>
     <t>0779305160</t>
   </si>
   <si>
     <t>NGOMA NIGEL</t>
   </si>
   <si>
-    <t>2024/77</t>
-  </si>
-  <si>
     <t>0771701987</t>
   </si>
   <si>
     <t>NDLOVU NEVILLE</t>
   </si>
   <si>
-    <t>2024/78</t>
-  </si>
-  <si>
     <t>0785600875</t>
   </si>
   <si>
     <t>NYONI RYAN</t>
   </si>
   <si>
-    <t>2024/79</t>
-  </si>
-  <si>
     <t>0779643223</t>
   </si>
   <si>
     <t>NDLOVU FUNDILE</t>
   </si>
   <si>
-    <t>2024/80</t>
-  </si>
-  <si>
     <t>0784316564</t>
   </si>
   <si>
     <t>NDLOVU HAMILTON</t>
   </si>
   <si>
-    <t>2024/81</t>
-  </si>
-  <si>
     <t>0772681990</t>
   </si>
   <si>
     <t>PHIRI ERIC</t>
   </si>
   <si>
-    <t>2024/82</t>
-  </si>
-  <si>
     <t>TRANSFERED</t>
   </si>
   <si>
     <t>SIBANDA LIONEL</t>
   </si>
   <si>
-    <t>2024/83</t>
-  </si>
-  <si>
     <t>0771322695</t>
   </si>
   <si>
     <t>SIBANDA DERRICK</t>
   </si>
   <si>
-    <t>2024/84</t>
-  </si>
-  <si>
     <t>Z0NDO INNOCENT</t>
   </si>
   <si>
-    <t>2024/85</t>
-  </si>
-  <si>
     <t>0783134468</t>
   </si>
   <si>
     <t>SIBANDA EMMANUEL</t>
   </si>
   <si>
-    <t>2024/86</t>
-  </si>
-  <si>
     <t>0780901752</t>
   </si>
   <si>
@@ -1674,54 +1150,33 @@
     <t>CHITUMBURA PALESA V</t>
   </si>
   <si>
-    <t>2023/01</t>
-  </si>
-  <si>
     <t>0780803987</t>
   </si>
   <si>
     <t>CHUMA BETTY</t>
   </si>
   <si>
-    <t>2023/02</t>
-  </si>
-  <si>
     <t>CHUMA NOKUTHULA</t>
   </si>
   <si>
-    <t>2023/03</t>
-  </si>
-  <si>
     <t>0785628072</t>
   </si>
   <si>
     <t>ISSA REJOICE</t>
   </si>
   <si>
-    <t>2023/04</t>
-  </si>
-  <si>
     <t>0779683077</t>
   </si>
   <si>
     <t>MAGUMA TINA</t>
   </si>
   <si>
-    <t>2023/05</t>
-  </si>
-  <si>
     <t>MAZANA TODDLEY</t>
   </si>
   <si>
-    <t>2023/06</t>
-  </si>
-  <si>
     <t>MHLANGA REJOICE</t>
   </si>
   <si>
-    <t>2023/07</t>
-  </si>
-  <si>
     <t>0786799634</t>
   </si>
   <si>
@@ -1731,96 +1186,60 @@
     <t>MLALAZI ZANELE</t>
   </si>
   <si>
-    <t>2023/08</t>
-  </si>
-  <si>
     <t>MILE MIRRIAM</t>
   </si>
   <si>
-    <t>2023/09</t>
-  </si>
-  <si>
     <t>0778715958</t>
   </si>
   <si>
     <t>MOYO BEYONCE</t>
   </si>
   <si>
-    <t>2023/10</t>
-  </si>
-  <si>
     <t>0785408925</t>
   </si>
   <si>
     <t>NCUBE NICOLE</t>
   </si>
   <si>
-    <t>2023/11</t>
-  </si>
-  <si>
     <t>SOLON                                  0</t>
   </si>
   <si>
     <t>NCUBE SHARON</t>
   </si>
   <si>
-    <t>2023/12</t>
-  </si>
-  <si>
     <t xml:space="preserve"> BEAM    TRANSFERED</t>
   </si>
   <si>
     <t>NDLOVU NTOKOZO</t>
   </si>
   <si>
-    <t>2023/13</t>
-  </si>
-  <si>
-    <t>2023/14</t>
-  </si>
-  <si>
     <t>NDLOVU SHALOM</t>
   </si>
   <si>
-    <t>2023/15</t>
-  </si>
-  <si>
     <t>0784592409</t>
   </si>
   <si>
     <t>NGWENYA EMILY T</t>
   </si>
   <si>
-    <t>2023/16</t>
-  </si>
-  <si>
     <t>0776237419</t>
   </si>
   <si>
     <t>NGWENYA BUHLEBENKOSI</t>
   </si>
   <si>
-    <t>2023/17</t>
-  </si>
-  <si>
     <t>0784243078</t>
   </si>
   <si>
     <t>NYATHI PROVIDENCE</t>
   </si>
   <si>
-    <t>2023/18</t>
-  </si>
-  <si>
     <t>ROMAN CATHOLIC</t>
   </si>
   <si>
     <t>NYONI PRIVILEDGE</t>
   </si>
   <si>
-    <t>2023/19</t>
-  </si>
-  <si>
     <t>0773489180</t>
   </si>
   <si>
@@ -1830,180 +1249,114 @@
     <t>PHIRI VIMBAINASHE</t>
   </si>
   <si>
-    <t>2023/20</t>
-  </si>
-  <si>
     <t>SHOKO VIOLET</t>
   </si>
   <si>
-    <t>2023/21</t>
-  </si>
-  <si>
     <t>0789283947</t>
   </si>
   <si>
     <t>SIAMANGAMU FLORENCE A</t>
   </si>
   <si>
-    <t>2023/22</t>
-  </si>
-  <si>
     <t>SIBANDA MELLISA A</t>
   </si>
   <si>
-    <t>2023/23</t>
-  </si>
-  <si>
     <t>0783130088</t>
   </si>
   <si>
     <t>SIFAYA BOKANI Z</t>
   </si>
   <si>
-    <t>2023/24</t>
-  </si>
-  <si>
     <t>0784586757</t>
   </si>
   <si>
     <t>DUBE SHYLET</t>
   </si>
   <si>
-    <t>2023/25</t>
-  </si>
-  <si>
     <t>0788340568</t>
   </si>
   <si>
     <t>DUBE SHYLEEN</t>
   </si>
   <si>
-    <t>2023/26</t>
-  </si>
-  <si>
     <t>MASUKU CASANDRA</t>
   </si>
   <si>
-    <t>2023/27</t>
-  </si>
-  <si>
     <t>0775230186</t>
   </si>
   <si>
     <t>MOYO PAMELA</t>
   </si>
   <si>
-    <t>2023/28</t>
-  </si>
-  <si>
     <t>0775643401</t>
   </si>
   <si>
     <t>CHUMA TAKUDZWA</t>
   </si>
   <si>
-    <t>2023/29</t>
-  </si>
-  <si>
     <t>0775668253</t>
   </si>
   <si>
     <t>GUMEDE KELVIN</t>
   </si>
   <si>
-    <t>2023/30</t>
-  </si>
-  <si>
     <t>JONES TERRY J</t>
   </si>
   <si>
-    <t>2023/31</t>
-  </si>
-  <si>
     <t>0772263962</t>
   </si>
   <si>
     <t>LUSINGA SHAWN</t>
   </si>
   <si>
-    <t>2023/32</t>
-  </si>
-  <si>
     <t>0772465449</t>
   </si>
   <si>
     <t>MATONGO NGONIDZASHE</t>
   </si>
   <si>
-    <t>2023/33</t>
-  </si>
-  <si>
     <t>0771322660</t>
   </si>
   <si>
     <t>MULEYA MUYAKI</t>
   </si>
   <si>
-    <t>2023/34</t>
-  </si>
-  <si>
     <t>MWAMBA DELVIN</t>
   </si>
   <si>
-    <t>2023/35</t>
-  </si>
-  <si>
     <t>0776051188</t>
   </si>
   <si>
     <t>NCUBE DENZEL</t>
   </si>
   <si>
-    <t>2023/36</t>
-  </si>
-  <si>
     <t>0775416146</t>
   </si>
   <si>
     <t>NCUBE NHLANHLA</t>
   </si>
   <si>
-    <t>2023/37</t>
-  </si>
-  <si>
     <t>0779013646</t>
   </si>
   <si>
     <t>NCUBE NKOSIZILE</t>
   </si>
   <si>
-    <t>2023/38</t>
-  </si>
-  <si>
     <t>0783226730</t>
   </si>
   <si>
     <t>NCUBE PRAYMORE</t>
   </si>
   <si>
-    <t>2023/39</t>
-  </si>
-  <si>
     <t>NDLOVU IAN</t>
   </si>
   <si>
-    <t>2023/40</t>
-  </si>
-  <si>
     <t>0772509928</t>
   </si>
   <si>
     <t>NYONI JUNIOR</t>
   </si>
   <si>
-    <t>2023/41</t>
-  </si>
-  <si>
     <t>0774659655</t>
   </si>
   <si>
@@ -2013,45 +1366,27 @@
     <t>SHOKO PROMISE</t>
   </si>
   <si>
-    <t>2023/42</t>
-  </si>
-  <si>
     <t>SIBANDA KISHER</t>
   </si>
   <si>
-    <t>2023/43</t>
-  </si>
-  <si>
     <t>SIBANDA SIPHAMANDLA</t>
   </si>
   <si>
-    <t>2023/44</t>
-  </si>
-  <si>
     <t>0785633292</t>
   </si>
   <si>
     <t>SINOYA BRIAN T</t>
   </si>
   <si>
-    <t>2023/45</t>
-  </si>
-  <si>
     <t>SINOYA DENZEL</t>
   </si>
   <si>
-    <t>2023/46</t>
-  </si>
-  <si>
     <t>0772465743</t>
   </si>
   <si>
     <t>VICTOR WISDOM</t>
   </si>
   <si>
-    <t>2023/47</t>
-  </si>
-  <si>
     <t>0781025564</t>
   </si>
   <si>
@@ -2061,15 +1396,9 @@
     <t>CHIMBUDZI TINASHE</t>
   </si>
   <si>
-    <t>2023/48</t>
-  </si>
-  <si>
     <t>NHDLOVU SHEPHERD</t>
   </si>
   <si>
-    <t>2023/49</t>
-  </si>
-  <si>
     <t>0785361520</t>
   </si>
   <si>
@@ -2082,9 +1411,6 @@
     <t>BANDURE HENRIETTA A</t>
   </si>
   <si>
-    <t>2023/51</t>
-  </si>
-  <si>
     <t>0773608817</t>
   </si>
   <si>
@@ -2094,120 +1420,75 @@
     <t>MABASA RUTENDO L</t>
   </si>
   <si>
-    <t>2023/52</t>
-  </si>
-  <si>
     <t>0777589644</t>
   </si>
   <si>
     <t>MAPHOSA CHARISMA T</t>
   </si>
   <si>
-    <t>2023/53</t>
-  </si>
-  <si>
     <t>0778108745</t>
   </si>
   <si>
     <t>MOYO SANDULELO</t>
   </si>
   <si>
-    <t>2023/54</t>
-  </si>
-  <si>
     <t>0784957062</t>
   </si>
   <si>
     <t>MUDENDA RANNY O</t>
   </si>
   <si>
-    <t>2023/55</t>
-  </si>
-  <si>
     <t>0773731896</t>
   </si>
   <si>
     <t>MADZIMA PRISCA</t>
   </si>
   <si>
-    <t>2023/56</t>
-  </si>
-  <si>
     <t>0713994672</t>
   </si>
   <si>
     <t>MULEYA TAPELO</t>
   </si>
   <si>
-    <t>2023/57</t>
-  </si>
-  <si>
     <t>0778814019</t>
   </si>
   <si>
     <t>MATHE PETITION</t>
   </si>
   <si>
-    <t>2023/58</t>
-  </si>
-  <si>
     <t>MOYO NOMSA</t>
   </si>
   <si>
-    <t>2023/59</t>
-  </si>
-  <si>
     <t>MPALA HENRIETTER T</t>
   </si>
   <si>
-    <t>2023/60</t>
-  </si>
-  <si>
     <t>MULEYA CATHRINE</t>
   </si>
   <si>
-    <t>2023/61</t>
-  </si>
-  <si>
     <t>0779145118</t>
   </si>
   <si>
     <t>MWAYENGA CHRISTINE</t>
   </si>
   <si>
-    <t>2023/62</t>
-  </si>
-  <si>
     <t>MWINDE PERSPICUOS B</t>
   </si>
   <si>
-    <t>2023/63</t>
-  </si>
-  <si>
     <t>NCUBE AYANDA K</t>
   </si>
   <si>
-    <t>2023/64</t>
-  </si>
-  <si>
     <t>SOLON                        42</t>
   </si>
   <si>
     <t>NCUBE BERTIN</t>
   </si>
   <si>
-    <t>2023/65</t>
-  </si>
-  <si>
     <t>0773890774</t>
   </si>
   <si>
     <t>NDABA JUDITH</t>
   </si>
   <si>
-    <t>2023/66</t>
-  </si>
-  <si>
     <t>078374743</t>
   </si>
   <si>
@@ -2217,42 +1498,27 @@
     <t>NDLOVU VUMANI</t>
   </si>
   <si>
-    <t>2023/67</t>
-  </si>
-  <si>
     <t>0788117470</t>
   </si>
   <si>
     <t xml:space="preserve">NDLOVU GLADYS </t>
   </si>
   <si>
-    <t>2023/68</t>
-  </si>
-  <si>
     <t>NGWENYA KWANDOKUHLE</t>
   </si>
   <si>
-    <t>2023/69</t>
-  </si>
-  <si>
     <t>0775257532</t>
   </si>
   <si>
     <t>NDEBELE WYETH</t>
   </si>
   <si>
-    <t>2023/70</t>
-  </si>
-  <si>
     <t>0779551486</t>
   </si>
   <si>
     <t>SIBANDA THANDOLWENKOSI</t>
   </si>
   <si>
-    <t>2023/71</t>
-  </si>
-  <si>
     <t>0782163420</t>
   </si>
   <si>
@@ -2262,27 +1528,18 @@
     <t>SIWELA BLESSING</t>
   </si>
   <si>
-    <t>2023/72</t>
-  </si>
-  <si>
     <t>0775437407</t>
   </si>
   <si>
     <t>TSHUMA DEPHINE</t>
   </si>
   <si>
-    <t>2023/73</t>
-  </si>
-  <si>
     <t>0788859982</t>
   </si>
   <si>
     <t>NGWENYA CYNTHIA</t>
   </si>
   <si>
-    <t>2023/74</t>
-  </si>
-  <si>
     <t>DZIRIPI JEREMIAH M</t>
   </si>
   <si>
@@ -2478,222 +1735,144 @@
     <t>MAGADZIRE CHARMAINE</t>
   </si>
   <si>
-    <t>2022/01</t>
-  </si>
-  <si>
     <t>0774838389</t>
   </si>
   <si>
     <t>MATHE SIMELINKOSI</t>
   </si>
   <si>
-    <t>2022/02</t>
-  </si>
-  <si>
     <t>0775657066</t>
   </si>
   <si>
     <t xml:space="preserve">MHAMBA ANNATONIA </t>
   </si>
   <si>
-    <t>2022/03</t>
-  </si>
-  <si>
     <t>0779993486</t>
   </si>
   <si>
     <t>MOYO ZANELE S</t>
   </si>
   <si>
-    <t>2022/04</t>
-  </si>
-  <si>
     <t>0775437126</t>
   </si>
   <si>
     <t>MPOFU GRACE</t>
   </si>
   <si>
-    <t>2022/05</t>
-  </si>
-  <si>
     <t>0782009892</t>
   </si>
   <si>
     <t>MWEMBE LULEKELELO</t>
   </si>
   <si>
-    <t>2022/06</t>
-  </si>
-  <si>
     <t>NCUBE SIMOMOTHEKILE</t>
   </si>
   <si>
-    <t>2022/07</t>
-  </si>
-  <si>
     <t>0782307911</t>
   </si>
   <si>
     <t>NDLOVU GRACE</t>
   </si>
   <si>
-    <t>2022/08</t>
-  </si>
-  <si>
     <t>0776313609</t>
   </si>
   <si>
     <t>NDLOVU CHARITY</t>
   </si>
   <si>
-    <t>2022/09</t>
-  </si>
-  <si>
     <t>0774478855</t>
   </si>
   <si>
     <t>SENGAI TINOFARA</t>
   </si>
   <si>
-    <t>2022/10</t>
-  </si>
-  <si>
     <t>0714037584</t>
   </si>
   <si>
     <t>SIBANDA AILEEN</t>
   </si>
   <si>
-    <t>2022/11</t>
-  </si>
-  <si>
     <t>0783447780</t>
   </si>
   <si>
     <t>SIBANDA FAITH</t>
   </si>
   <si>
-    <t>2022/12</t>
-  </si>
-  <si>
     <t>CHITUMBURA VINCLEE</t>
   </si>
   <si>
-    <t>2022/13</t>
-  </si>
-  <si>
     <t>0782163290</t>
   </si>
   <si>
     <t>CHUMA PROMINENCE</t>
   </si>
   <si>
-    <t>2022/14</t>
-  </si>
-  <si>
     <t>0780334093</t>
   </si>
   <si>
     <t>DUBE HONEST</t>
   </si>
   <si>
-    <t>2022/15</t>
-  </si>
-  <si>
     <t>0782163220</t>
   </si>
   <si>
     <t>FOX CHRISTOPHER</t>
   </si>
   <si>
-    <t>2022/16</t>
-  </si>
-  <si>
     <t>0782009908</t>
   </si>
   <si>
     <t>MABASO FORTUNE</t>
   </si>
   <si>
-    <t>2022/17</t>
-  </si>
-  <si>
     <t>0775257726</t>
   </si>
   <si>
     <t>MACHECHE MATHIAS</t>
   </si>
   <si>
-    <t>2022/18</t>
-  </si>
-  <si>
     <t>0783071680</t>
   </si>
   <si>
     <t>MAPAKO TASHINGA</t>
   </si>
   <si>
-    <t>2022/19</t>
-  </si>
-  <si>
     <t>0775136172</t>
   </si>
   <si>
     <t>MATHE THAMSANQA</t>
   </si>
   <si>
-    <t>2022/20</t>
-  </si>
-  <si>
     <t>0781901588</t>
   </si>
   <si>
     <t>MHLANGA RICHARD</t>
   </si>
   <si>
-    <t>2022/21</t>
-  </si>
-  <si>
     <t>MILAZI PANASHE</t>
   </si>
   <si>
-    <t>2022/22</t>
-  </si>
-  <si>
     <t>0778671557</t>
   </si>
   <si>
     <t>MOYO ELVIS</t>
   </si>
   <si>
-    <t>2022/23</t>
-  </si>
-  <si>
     <t>0779013952</t>
   </si>
   <si>
     <t>MOYO GOODTIDINGS</t>
   </si>
   <si>
-    <t>2022/24</t>
-  </si>
-  <si>
     <t>BEAM             140</t>
   </si>
   <si>
     <t>MOYO NKOSILATHI</t>
   </si>
   <si>
-    <t>2022/25</t>
-  </si>
-  <si>
     <t>MOYO THEMBELANI</t>
   </si>
   <si>
-    <t>2022/26</t>
-  </si>
-  <si>
     <t>0712251274</t>
   </si>
   <si>
@@ -2703,102 +1882,63 @@
     <t>MPALA SIMBARASHE</t>
   </si>
   <si>
-    <t>2022/27</t>
-  </si>
-  <si>
     <t>NCUBE FORTUNE</t>
   </si>
   <si>
-    <t>2022/28</t>
-  </si>
-  <si>
     <t>NCUBE MANDLA</t>
   </si>
   <si>
-    <t>2022/29</t>
-  </si>
-  <si>
     <t>0784201147</t>
   </si>
   <si>
     <t>NDLOVU RICKY</t>
   </si>
   <si>
-    <t>2022/30</t>
-  </si>
-  <si>
     <t>0715376663</t>
   </si>
   <si>
     <t>NGOMA ANNORD</t>
   </si>
   <si>
-    <t>2022/31</t>
-  </si>
-  <si>
     <t>0775629085</t>
   </si>
   <si>
     <t>NGWENYA WITNESS</t>
   </si>
   <si>
-    <t>2022/32</t>
-  </si>
-  <si>
     <t>NKOMO BRENDON</t>
   </si>
   <si>
-    <t>2022/33</t>
-  </si>
-  <si>
     <t>0774389243</t>
   </si>
   <si>
     <t>NYAMA PRESLEY</t>
   </si>
   <si>
-    <t>2022/34</t>
-  </si>
-  <si>
     <t>NYONI LEONEL</t>
   </si>
   <si>
-    <t>2022/35</t>
-  </si>
-  <si>
     <t>0785406586</t>
   </si>
   <si>
     <t>SHAMUYASHE BLOOM</t>
   </si>
   <si>
-    <t>2022/36</t>
-  </si>
-  <si>
     <t>0771134864</t>
   </si>
   <si>
     <t>SIBANDA BLESSING</t>
   </si>
   <si>
-    <t>2022/37</t>
-  </si>
-  <si>
     <t>MATONGO BLESSING</t>
   </si>
   <si>
-    <t>2022/38</t>
-  </si>
-  <si>
     <t>FORM 4 NORTH FEES REGISTER</t>
   </si>
   <si>
     <t>BAZANGE LORRAINE</t>
   </si>
   <si>
-    <t>2022/39</t>
-  </si>
-  <si>
     <t>0775162224</t>
   </si>
   <si>
@@ -2808,18 +1948,12 @@
     <t>BEBULO RUVARASHE</t>
   </si>
   <si>
-    <t>2022/40</t>
-  </si>
-  <si>
     <t>0771143416</t>
   </si>
   <si>
     <t>CHITUNGWA SANDISIWE</t>
   </si>
   <si>
-    <t>2022/41</t>
-  </si>
-  <si>
     <t>0778784663</t>
   </si>
   <si>
@@ -2829,111 +1963,69 @@
     <t>DUBE LONDILE</t>
   </si>
   <si>
-    <t>2022/42</t>
-  </si>
-  <si>
     <t>HAID ANESU</t>
   </si>
   <si>
-    <t>2022/43</t>
-  </si>
-  <si>
     <t>KANAMA MARTHA</t>
   </si>
   <si>
-    <t>2022/44</t>
-  </si>
-  <si>
     <t>0783690194</t>
   </si>
   <si>
     <t>KHUPHE BELINDA</t>
   </si>
   <si>
-    <t>2022/45</t>
-  </si>
-  <si>
     <t>0787849760</t>
   </si>
   <si>
     <t>LUNGA INNOCENCIA</t>
   </si>
   <si>
-    <t>2022/46</t>
-  </si>
-  <si>
     <t>MAKINZE MITCHEL</t>
   </si>
   <si>
-    <t>2022/47</t>
-  </si>
-  <si>
     <t>0775878355</t>
   </si>
   <si>
     <t>MANDEBVU NTOMBIKAYISE</t>
   </si>
   <si>
-    <t>2022/48</t>
-  </si>
-  <si>
     <t>MAVEZA AUDREY</t>
   </si>
   <si>
-    <t>2022/49</t>
-  </si>
-  <si>
     <t>0784970671</t>
   </si>
   <si>
     <t>MBEVE BRIDGET</t>
   </si>
   <si>
-    <t>2022/50</t>
-  </si>
-  <si>
     <t>0777479020</t>
   </si>
   <si>
     <t>MOYO PATIENCE</t>
   </si>
   <si>
-    <t>2022/51</t>
-  </si>
-  <si>
     <t>MUDIMBA PERCULIAR</t>
   </si>
   <si>
-    <t>2022/52</t>
-  </si>
-  <si>
     <t>0711778895</t>
   </si>
   <si>
     <t>NDLOVU ALICIA</t>
   </si>
   <si>
-    <t>2022/53</t>
-  </si>
-  <si>
     <t>0776169498</t>
   </si>
   <si>
     <t>NGWENYA HELLEN</t>
   </si>
   <si>
-    <t>2022/54</t>
-  </si>
-  <si>
     <t>0778248276</t>
   </si>
   <si>
     <t>NGWENYA TANYARADZWA</t>
   </si>
   <si>
-    <t>2022/55</t>
-  </si>
-  <si>
     <t>0785516828</t>
   </si>
   <si>
@@ -2943,18 +2035,12 @@
     <t>NYATHI MBALENHLE</t>
   </si>
   <si>
-    <t>2022/56</t>
-  </si>
-  <si>
     <t>0778135517</t>
   </si>
   <si>
     <t>NYONI VANNESSA</t>
   </si>
   <si>
-    <t>2022/57</t>
-  </si>
-  <si>
     <t>0775239854</t>
   </si>
   <si>
@@ -2964,9 +2050,6 @@
     <t>PHAHLANE LETICIA</t>
   </si>
   <si>
-    <t>2022/58</t>
-  </si>
-  <si>
     <t>0775437416</t>
   </si>
   <si>
@@ -2976,164 +2059,1088 @@
     <t>SIBELO MARLEY</t>
   </si>
   <si>
-    <t>2022/59</t>
-  </si>
-  <si>
     <t>DUBE ANNATONIA</t>
   </si>
   <si>
-    <t>2022/77</t>
-  </si>
-  <si>
     <t>0774417251</t>
   </si>
   <si>
     <t>CHIMURAMBA SHEPHERD T</t>
   </si>
   <si>
-    <t>2022/60</t>
-  </si>
-  <si>
     <t>0785462088</t>
   </si>
   <si>
     <t>CHITUNGWA ANDILE</t>
   </si>
   <si>
-    <t>2022/61</t>
-  </si>
-  <si>
     <t>CHUMA LEEROY</t>
   </si>
   <si>
-    <t>2022/62</t>
-  </si>
-  <si>
     <t>0772251128</t>
   </si>
   <si>
     <t>DUBE PROUD</t>
   </si>
   <si>
-    <t>2022/63</t>
-  </si>
-  <si>
     <t>MANDIZIVA SIBUSISO</t>
   </si>
   <si>
-    <t>2022/64</t>
-  </si>
-  <si>
     <t>0785408098</t>
   </si>
   <si>
     <t>MASUKU BRIGHT</t>
   </si>
   <si>
-    <t>2022/65</t>
-  </si>
-  <si>
     <t>0785392559</t>
   </si>
   <si>
     <t>MATUTU ALLAN</t>
   </si>
   <si>
-    <t>2022/66</t>
-  </si>
-  <si>
     <t>0786035459</t>
   </si>
   <si>
     <t>MDLONGWA MAOKETSI</t>
   </si>
   <si>
-    <t>2022/67</t>
-  </si>
-  <si>
     <t>0782133065</t>
   </si>
   <si>
     <t>MNKANDLA THAMSANQA</t>
   </si>
   <si>
-    <t>2022/68</t>
-  </si>
-  <si>
     <t>0784956016</t>
   </si>
   <si>
     <t>MOYO CUETA</t>
   </si>
   <si>
-    <t>2022/69</t>
-  </si>
-  <si>
     <t>SOLON                        21</t>
   </si>
   <si>
     <t>MUSEVA SHAIN</t>
   </si>
   <si>
-    <t>2022/70</t>
-  </si>
-  <si>
     <t>0777097367</t>
   </si>
   <si>
     <t>NCUBE ADMIRE</t>
   </si>
   <si>
-    <t>2022/71</t>
-  </si>
-  <si>
     <t>0785547504</t>
   </si>
   <si>
     <t>NKHOMA BRIAN</t>
   </si>
   <si>
-    <t>2022/72</t>
-  </si>
-  <si>
     <t>0776313647</t>
   </si>
   <si>
     <t>SIBANDA BRIGHT</t>
   </si>
   <si>
-    <t>2022/73</t>
-  </si>
-  <si>
     <t>0779527674</t>
   </si>
   <si>
     <t>SIBANDA KWAZINKOSI</t>
   </si>
   <si>
-    <t>2022/74</t>
-  </si>
-  <si>
     <t>0782535533</t>
   </si>
   <si>
     <t>TSHAKA PROFESSOR</t>
   </si>
   <si>
-    <t>2022/75</t>
-  </si>
-  <si>
     <t>MUNSAKA KEITHBOY</t>
   </si>
   <si>
-    <t>2022/76</t>
+    <t>DET-2025-001</t>
+  </si>
+  <si>
+    <t>DET-2025-002</t>
+  </si>
+  <si>
+    <t>DET-2025-003</t>
+  </si>
+  <si>
+    <t>DET-2025-004</t>
+  </si>
+  <si>
+    <t>DET-2025-005</t>
+  </si>
+  <si>
+    <t>DET-2025-006</t>
+  </si>
+  <si>
+    <t>DET-2025-007</t>
+  </si>
+  <si>
+    <t>DET-2025-008</t>
+  </si>
+  <si>
+    <t>DET-2025-009</t>
+  </si>
+  <si>
+    <t>DET-2025-010</t>
+  </si>
+  <si>
+    <t>DET-2025-011</t>
+  </si>
+  <si>
+    <t>DET-2025-012</t>
+  </si>
+  <si>
+    <t>DET-2025-013</t>
+  </si>
+  <si>
+    <t>DET-2025-014</t>
+  </si>
+  <si>
+    <t>DET-2025-015</t>
+  </si>
+  <si>
+    <t>DET-2025-016</t>
+  </si>
+  <si>
+    <t>DET-2025-017</t>
+  </si>
+  <si>
+    <t>DET-2025-018</t>
+  </si>
+  <si>
+    <t>DET-2025-019</t>
+  </si>
+  <si>
+    <t>DET-2025-020</t>
+  </si>
+  <si>
+    <t>DET-2025-021</t>
+  </si>
+  <si>
+    <t>DET-2025-022</t>
+  </si>
+  <si>
+    <t>DET-2025-023</t>
+  </si>
+  <si>
+    <t>DET-2025-024</t>
+  </si>
+  <si>
+    <t>DET-2025-025</t>
+  </si>
+  <si>
+    <t>DET-2025-026</t>
+  </si>
+  <si>
+    <t>DET-2025-027</t>
+  </si>
+  <si>
+    <t>DET-2025-028</t>
+  </si>
+  <si>
+    <t>DET-2025-029</t>
+  </si>
+  <si>
+    <t>DET-2025-030</t>
+  </si>
+  <si>
+    <t>DET-2025-031</t>
+  </si>
+  <si>
+    <t>DET-2025-032</t>
+  </si>
+  <si>
+    <t>DET-2025-033</t>
+  </si>
+  <si>
+    <t>DET-2025-034</t>
+  </si>
+  <si>
+    <t>DET-2025-035</t>
+  </si>
+  <si>
+    <t>DET-2025-036</t>
+  </si>
+  <si>
+    <t>DET-2025-037</t>
+  </si>
+  <si>
+    <t>DET-2025-038</t>
+  </si>
+  <si>
+    <t>DET-2025-039</t>
+  </si>
+  <si>
+    <t>DET-2025-040</t>
+  </si>
+  <si>
+    <t>DET-2025-041</t>
+  </si>
+  <si>
+    <t>DET-2025-042</t>
+  </si>
+  <si>
+    <t>DET-2025-043</t>
+  </si>
+  <si>
+    <t>DET-2025-044</t>
+  </si>
+  <si>
+    <t>DET-2025-045</t>
+  </si>
+  <si>
+    <t>DET-2025-046</t>
+  </si>
+  <si>
+    <t>DET-2025-047</t>
+  </si>
+  <si>
+    <t>DET-2025-048</t>
+  </si>
+  <si>
+    <t>DET-2025-049</t>
+  </si>
+  <si>
+    <t>DET-2025-050</t>
+  </si>
+  <si>
+    <t>DET-2025-051</t>
+  </si>
+  <si>
+    <t>DET-2025-052</t>
+  </si>
+  <si>
+    <t>DET-2025-053</t>
+  </si>
+  <si>
+    <t>DET-2025-054</t>
+  </si>
+  <si>
+    <t>DET-2025-055</t>
+  </si>
+  <si>
+    <t>DET-2025-056</t>
+  </si>
+  <si>
+    <t>DET-2025-057</t>
+  </si>
+  <si>
+    <t>DET-2025-058</t>
+  </si>
+  <si>
+    <t>DET-2025-059</t>
+  </si>
+  <si>
+    <t>DET-2025-060</t>
+  </si>
+  <si>
+    <t>DET-2025-061</t>
+  </si>
+  <si>
+    <t>DET-2025-062</t>
+  </si>
+  <si>
+    <t>DET-2025-063</t>
+  </si>
+  <si>
+    <t>DET-2025-064</t>
+  </si>
+  <si>
+    <t>DET-2025-065</t>
+  </si>
+  <si>
+    <t>DET-2025-066</t>
+  </si>
+  <si>
+    <t>DET-2025-067</t>
+  </si>
+  <si>
+    <t>DET-2025-068</t>
+  </si>
+  <si>
+    <t>DET-2025-069</t>
+  </si>
+  <si>
+    <t>DET-2025-070</t>
+  </si>
+  <si>
+    <t>DET-2025-071</t>
+  </si>
+  <si>
+    <t>DET-2025-072</t>
+  </si>
+  <si>
+    <t>DET-2025-073</t>
+  </si>
+  <si>
+    <t>DET-2025-074</t>
+  </si>
+  <si>
+    <t>DET-2025-075</t>
+  </si>
+  <si>
+    <t>DET-2025-076</t>
+  </si>
+  <si>
+    <t>DET-2025-077</t>
+  </si>
+  <si>
+    <t>DET-2025-078</t>
+  </si>
+  <si>
+    <t>DET-2025-079</t>
+  </si>
+  <si>
+    <t>DET-2025-080</t>
+  </si>
+  <si>
+    <t>DET-2025-081</t>
+  </si>
+  <si>
+    <t>DET-2025-082</t>
+  </si>
+  <si>
+    <t>DET-2025-083</t>
+  </si>
+  <si>
+    <t>DET-2025-084</t>
+  </si>
+  <si>
+    <t>DET-2025-085</t>
+  </si>
+  <si>
+    <t>DET-2025-086</t>
+  </si>
+  <si>
+    <t>DET-2025-087</t>
+  </si>
+  <si>
+    <t>DET-2024-001</t>
+  </si>
+  <si>
+    <t>DET-2024-002</t>
+  </si>
+  <si>
+    <t>DET-2024-003</t>
+  </si>
+  <si>
+    <t>DET-2024-004</t>
+  </si>
+  <si>
+    <t>DET-2024-005</t>
+  </si>
+  <si>
+    <t>DET-2024-006</t>
+  </si>
+  <si>
+    <t>DET-2024-007</t>
+  </si>
+  <si>
+    <t>DET-2024-008</t>
+  </si>
+  <si>
+    <t>DET-2024-009</t>
+  </si>
+  <si>
+    <t>DET-2024-010</t>
+  </si>
+  <si>
+    <t>DET-2024-011</t>
+  </si>
+  <si>
+    <t>DET-2024-012</t>
+  </si>
+  <si>
+    <t>DET-2024-013</t>
+  </si>
+  <si>
+    <t>DET-2024-014</t>
+  </si>
+  <si>
+    <t>DET-2024-015</t>
+  </si>
+  <si>
+    <t>DET-2024-016</t>
+  </si>
+  <si>
+    <t>DET-2024-017</t>
+  </si>
+  <si>
+    <t>DET-2024-018</t>
+  </si>
+  <si>
+    <t>DET-2024-019</t>
+  </si>
+  <si>
+    <t>DET-2024-020</t>
+  </si>
+  <si>
+    <t>DET-2024-021</t>
+  </si>
+  <si>
+    <t>DET-2024-022</t>
+  </si>
+  <si>
+    <t>DET-2024-023</t>
+  </si>
+  <si>
+    <t>DET-2024-024</t>
+  </si>
+  <si>
+    <t>DET-2024-025</t>
+  </si>
+  <si>
+    <t>DET-2024-026</t>
+  </si>
+  <si>
+    <t>DET-2024-027</t>
+  </si>
+  <si>
+    <t>DET-2024-028</t>
+  </si>
+  <si>
+    <t>DET-2024-029</t>
+  </si>
+  <si>
+    <t>DET-2024-030</t>
+  </si>
+  <si>
+    <t>DET-2024-031</t>
+  </si>
+  <si>
+    <t>DET-2024-032</t>
+  </si>
+  <si>
+    <t>DET-2024-033</t>
+  </si>
+  <si>
+    <t>DET-2024-034</t>
+  </si>
+  <si>
+    <t>DET-2024-035</t>
+  </si>
+  <si>
+    <t>DET-2024-036</t>
+  </si>
+  <si>
+    <t>DET-2024-037</t>
+  </si>
+  <si>
+    <t>DET-2024-038</t>
+  </si>
+  <si>
+    <t>DET-2024-039</t>
+  </si>
+  <si>
+    <t>DET-2024-040</t>
+  </si>
+  <si>
+    <t>DET-2024-041</t>
+  </si>
+  <si>
+    <t>DET-2024-042</t>
+  </si>
+  <si>
+    <t>DET-2024-043</t>
+  </si>
+  <si>
+    <t>DET-2024-044</t>
+  </si>
+  <si>
+    <t>DET-2024-045</t>
+  </si>
+  <si>
+    <t>DET-2024-046</t>
+  </si>
+  <si>
+    <t>DET-2024-047</t>
+  </si>
+  <si>
+    <t>DET-2024-048</t>
+  </si>
+  <si>
+    <t>DET-2024-049</t>
+  </si>
+  <si>
+    <t>DET-2024-050</t>
+  </si>
+  <si>
+    <t>DET-2024-051</t>
+  </si>
+  <si>
+    <t>DET-2024-052</t>
+  </si>
+  <si>
+    <t>DET-2024-053</t>
+  </si>
+  <si>
+    <t>DET-2024-054</t>
+  </si>
+  <si>
+    <t>DET-2024-055</t>
+  </si>
+  <si>
+    <t>DET-2024-056</t>
+  </si>
+  <si>
+    <t>DET-2024-057</t>
+  </si>
+  <si>
+    <t>DET-2024-058</t>
+  </si>
+  <si>
+    <t>DET-2024-059</t>
+  </si>
+  <si>
+    <t>DET-2024-060</t>
+  </si>
+  <si>
+    <t>DET-2024-061</t>
+  </si>
+  <si>
+    <t>DET-2024-062</t>
+  </si>
+  <si>
+    <t>DET-2024-063</t>
+  </si>
+  <si>
+    <t>DET-2024-064</t>
+  </si>
+  <si>
+    <t>DET-2024-065</t>
+  </si>
+  <si>
+    <t>DET-2024-066</t>
+  </si>
+  <si>
+    <t>DET-2024-067</t>
+  </si>
+  <si>
+    <t>DET-2024-068</t>
+  </si>
+  <si>
+    <t>DET-2024-069</t>
+  </si>
+  <si>
+    <t>DET-2024-070</t>
+  </si>
+  <si>
+    <t>DET-2024-071</t>
+  </si>
+  <si>
+    <t>DET-2024-072</t>
+  </si>
+  <si>
+    <t>DET-2024-073</t>
+  </si>
+  <si>
+    <t>DET-2024-074</t>
+  </si>
+  <si>
+    <t>DET-2024-075</t>
+  </si>
+  <si>
+    <t>DET-2024-076</t>
+  </si>
+  <si>
+    <t>DET-2024-077</t>
+  </si>
+  <si>
+    <t>DET-2024-078</t>
+  </si>
+  <si>
+    <t>DET-2024-079</t>
+  </si>
+  <si>
+    <t>DET-2024-080</t>
+  </si>
+  <si>
+    <t>DET-2024-081</t>
+  </si>
+  <si>
+    <t>DET-2024-082</t>
+  </si>
+  <si>
+    <t>DET-2024-083</t>
+  </si>
+  <si>
+    <t>DET-2024-084</t>
+  </si>
+  <si>
+    <t>DET-2024-085</t>
+  </si>
+  <si>
+    <t>DET-2024-086</t>
+  </si>
+  <si>
+    <t>DET-2024-087</t>
+  </si>
+  <si>
+    <t>DET-2024-088</t>
+  </si>
+  <si>
+    <t>DET-2024-089</t>
+  </si>
+  <si>
+    <t>DET-2024-090</t>
+  </si>
+  <si>
+    <t>DET-2023-001</t>
+  </si>
+  <si>
+    <t>DET-2023-002</t>
+  </si>
+  <si>
+    <t>DET-2023-003</t>
+  </si>
+  <si>
+    <t>DET-2023-004</t>
+  </si>
+  <si>
+    <t>DET-2023-005</t>
+  </si>
+  <si>
+    <t>DET-2023-006</t>
+  </si>
+  <si>
+    <t>DET-2023-007</t>
+  </si>
+  <si>
+    <t>DET-2023-008</t>
+  </si>
+  <si>
+    <t>DET-2023-009</t>
+  </si>
+  <si>
+    <t>DET-2023-010</t>
+  </si>
+  <si>
+    <t>DET-2023-011</t>
+  </si>
+  <si>
+    <t>DET-2023-012</t>
+  </si>
+  <si>
+    <t>DET-2023-013</t>
+  </si>
+  <si>
+    <t>DET-2023-014</t>
+  </si>
+  <si>
+    <t>DET-2023-015</t>
+  </si>
+  <si>
+    <t>DET-2023-016</t>
+  </si>
+  <si>
+    <t>DET-2023-017</t>
+  </si>
+  <si>
+    <t>DET-2023-018</t>
+  </si>
+  <si>
+    <t>DET-2023-019</t>
+  </si>
+  <si>
+    <t>DET-2023-020</t>
+  </si>
+  <si>
+    <t>DET-2023-021</t>
+  </si>
+  <si>
+    <t>DET-2023-022</t>
+  </si>
+  <si>
+    <t>DET-2023-023</t>
+  </si>
+  <si>
+    <t>DET-2023-024</t>
+  </si>
+  <si>
+    <t>DET-2023-025</t>
+  </si>
+  <si>
+    <t>DET-2023-026</t>
+  </si>
+  <si>
+    <t>DET-2023-027</t>
+  </si>
+  <si>
+    <t>DET-2023-028</t>
+  </si>
+  <si>
+    <t>DET-2023-029</t>
+  </si>
+  <si>
+    <t>DET-2023-030</t>
+  </si>
+  <si>
+    <t>DET-2023-031</t>
+  </si>
+  <si>
+    <t>DET-2023-032</t>
+  </si>
+  <si>
+    <t>DET-2023-033</t>
+  </si>
+  <si>
+    <t>DET-2023-034</t>
+  </si>
+  <si>
+    <t>DET-2023-035</t>
+  </si>
+  <si>
+    <t>DET-2023-036</t>
+  </si>
+  <si>
+    <t>DET-2023-037</t>
+  </si>
+  <si>
+    <t>DET-2023-038</t>
+  </si>
+  <si>
+    <t>DET-2023-039</t>
+  </si>
+  <si>
+    <t>DET-2023-040</t>
+  </si>
+  <si>
+    <t>DET-2023-041</t>
+  </si>
+  <si>
+    <t>DET-2023-042</t>
+  </si>
+  <si>
+    <t>DET-2023-043</t>
+  </si>
+  <si>
+    <t>DET-2023-044</t>
+  </si>
+  <si>
+    <t>DET-2023-045</t>
+  </si>
+  <si>
+    <t>DET-2023-046</t>
+  </si>
+  <si>
+    <t>DET-2023-047</t>
+  </si>
+  <si>
+    <t>DET-2023-048</t>
+  </si>
+  <si>
+    <t>DET-2023-049</t>
+  </si>
+  <si>
+    <t>DET-2023-050</t>
+  </si>
+  <si>
+    <t>DET-2023-051</t>
+  </si>
+  <si>
+    <t>DET-2023-052</t>
+  </si>
+  <si>
+    <t>DET-2023-053</t>
+  </si>
+  <si>
+    <t>DET-2023-054</t>
+  </si>
+  <si>
+    <t>DET-2023-055</t>
+  </si>
+  <si>
+    <t>DET-2023-056</t>
+  </si>
+  <si>
+    <t>DET-2023-057</t>
+  </si>
+  <si>
+    <t>DET-2023-058</t>
+  </si>
+  <si>
+    <t>DET-2023-059</t>
+  </si>
+  <si>
+    <t>DET-2023-060</t>
+  </si>
+  <si>
+    <t>DET-2023-061</t>
+  </si>
+  <si>
+    <t>DET-2023-062</t>
+  </si>
+  <si>
+    <t>DET-2023-063</t>
+  </si>
+  <si>
+    <t>DET-2023-064</t>
+  </si>
+  <si>
+    <t>DET-2023-065</t>
+  </si>
+  <si>
+    <t>DET-2023-066</t>
+  </si>
+  <si>
+    <t>DET-2023-067</t>
+  </si>
+  <si>
+    <t>DET-2023-068</t>
+  </si>
+  <si>
+    <t>DET-2023-069</t>
+  </si>
+  <si>
+    <t>DET-2023-070</t>
+  </si>
+  <si>
+    <t>DET-2023-071</t>
+  </si>
+  <si>
+    <t>DET-2023-072</t>
+  </si>
+  <si>
+    <t>DET-2023-073</t>
+  </si>
+  <si>
+    <t>DET-2022-001</t>
+  </si>
+  <si>
+    <t>DET-2022-002</t>
+  </si>
+  <si>
+    <t>DET-2022-003</t>
+  </si>
+  <si>
+    <t>DET-2022-004</t>
+  </si>
+  <si>
+    <t>DET-2022-005</t>
+  </si>
+  <si>
+    <t>DET-2022-006</t>
+  </si>
+  <si>
+    <t>DET-2022-007</t>
+  </si>
+  <si>
+    <t>DET-2022-008</t>
+  </si>
+  <si>
+    <t>DET-2022-009</t>
+  </si>
+  <si>
+    <t>DET-2022-010</t>
+  </si>
+  <si>
+    <t>DET-2022-011</t>
+  </si>
+  <si>
+    <t>DET-2022-012</t>
+  </si>
+  <si>
+    <t>DET-2022-013</t>
+  </si>
+  <si>
+    <t>DET-2022-014</t>
+  </si>
+  <si>
+    <t>DET-2022-015</t>
+  </si>
+  <si>
+    <t>DET-2022-016</t>
+  </si>
+  <si>
+    <t>DET-2022-017</t>
+  </si>
+  <si>
+    <t>DET-2022-018</t>
+  </si>
+  <si>
+    <t>DET-2022-019</t>
+  </si>
+  <si>
+    <t>DET-2022-020</t>
+  </si>
+  <si>
+    <t>DET-2022-021</t>
+  </si>
+  <si>
+    <t>DET-2022-022</t>
+  </si>
+  <si>
+    <t>DET-2022-023</t>
+  </si>
+  <si>
+    <t>DET-2022-024</t>
+  </si>
+  <si>
+    <t>DET-2022-025</t>
+  </si>
+  <si>
+    <t>DET-2022-026</t>
+  </si>
+  <si>
+    <t>DET-2022-027</t>
+  </si>
+  <si>
+    <t>DET-2022-028</t>
+  </si>
+  <si>
+    <t>DET-2022-029</t>
+  </si>
+  <si>
+    <t>DET-2022-030</t>
+  </si>
+  <si>
+    <t>DET-2022-031</t>
+  </si>
+  <si>
+    <t>DET-2022-032</t>
+  </si>
+  <si>
+    <t>DET-2022-033</t>
+  </si>
+  <si>
+    <t>DET-2022-034</t>
+  </si>
+  <si>
+    <t>DET-2022-035</t>
+  </si>
+  <si>
+    <t>DET-2022-036</t>
+  </si>
+  <si>
+    <t>DET-2022-037</t>
+  </si>
+  <si>
+    <t>DET-2022-038</t>
+  </si>
+  <si>
+    <t>DET-2022-039</t>
+  </si>
+  <si>
+    <t>DET-2022-040</t>
+  </si>
+  <si>
+    <t>DET-2022-041</t>
+  </si>
+  <si>
+    <t>DET-2022-042</t>
+  </si>
+  <si>
+    <t>DET-2022-043</t>
+  </si>
+  <si>
+    <t>DET-2022-044</t>
+  </si>
+  <si>
+    <t>DET-2022-045</t>
+  </si>
+  <si>
+    <t>DET-2022-046</t>
+  </si>
+  <si>
+    <t>DET-2022-047</t>
+  </si>
+  <si>
+    <t>DET-2022-048</t>
+  </si>
+  <si>
+    <t>DET-2022-049</t>
+  </si>
+  <si>
+    <t>DET-2022-050</t>
+  </si>
+  <si>
+    <t>DET-2022-051</t>
+  </si>
+  <si>
+    <t>DET-2022-052</t>
+  </si>
+  <si>
+    <t>DET-2022-053</t>
+  </si>
+  <si>
+    <t>DET-2022-054</t>
+  </si>
+  <si>
+    <t>DET-2022-055</t>
+  </si>
+  <si>
+    <t>DET-2022-056</t>
+  </si>
+  <si>
+    <t>DET-2022-057</t>
+  </si>
+  <si>
+    <t>DET-2022-058</t>
+  </si>
+  <si>
+    <t>DET-2022-059</t>
+  </si>
+  <si>
+    <t>DET-2022-060</t>
+  </si>
+  <si>
+    <t>DET-2022-061</t>
+  </si>
+  <si>
+    <t>DET-2022-062</t>
+  </si>
+  <si>
+    <t>DET-2022-063</t>
+  </si>
+  <si>
+    <t>DET-2022-064</t>
+  </si>
+  <si>
+    <t>DET-2022-065</t>
+  </si>
+  <si>
+    <t>DET-2022-066</t>
+  </si>
+  <si>
+    <t>DET-2022-067</t>
+  </si>
+  <si>
+    <t>DET-2022-068</t>
+  </si>
+  <si>
+    <t>DET-2022-069</t>
+  </si>
+  <si>
+    <t>DET-2022-070</t>
+  </si>
+  <si>
+    <t>DET-2022-071</t>
+  </si>
+  <si>
+    <t>DET-2022-072</t>
+  </si>
+  <si>
+    <t>DET-2022-073</t>
+  </si>
+  <si>
+    <t>DET-2022-074</t>
+  </si>
+  <si>
+    <t>DET-2022-075</t>
+  </si>
+  <si>
+    <t>DET-2022-076</t>
+  </si>
+  <si>
+    <t>DET-2022-077</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3152,6 +3159,12 @@
       <i/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3749,10 +3762,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3763,13 +3776,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>706</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -3780,27 +3793,27 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>707</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>708</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>140</v>
@@ -3808,41 +3821,41 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>709</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>710</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>711</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -3850,16 +3863,16 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>712</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2">
         <v>21</v>
@@ -3867,13 +3880,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>713</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3881,13 +3894,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>714</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3898,13 +3911,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>715</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>40</v>
@@ -3915,27 +3928,27 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>716</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>717</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>30</v>
@@ -3946,13 +3959,13 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>718</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D16">
         <v>20</v>
@@ -3963,13 +3976,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>719</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -3980,13 +3993,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>720</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>70</v>
@@ -3994,13 +4007,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>721</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D19">
         <v>30</v>
@@ -4011,16 +4024,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>722</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2">
         <v>21</v>
@@ -4028,24 +4041,24 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>723</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>724</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>70</v>
@@ -4059,13 +4072,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>725</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D23">
         <v>120</v>
@@ -4076,13 +4089,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>726</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>70</v>
@@ -4090,10 +4103,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>727</v>
       </c>
       <c r="D29">
         <v>140</v>
@@ -4101,16 +4114,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>728</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2">
         <v>21</v>
@@ -4118,13 +4131,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>729</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D31">
         <v>140</v>
@@ -4132,13 +4145,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>730</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4149,27 +4162,27 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>731</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>732</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -4183,13 +4196,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>733</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D35">
         <v>50</v>
@@ -4200,13 +4213,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>734</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4217,13 +4230,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>735</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D37">
         <v>140</v>
@@ -4231,13 +4244,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>736</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D38">
         <v>60</v>
@@ -4248,13 +4261,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>737</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D39">
         <v>110</v>
@@ -4265,13 +4278,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>738</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D40">
         <v>100</v>
@@ -4279,27 +4292,27 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>739</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
+        <v>740</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D42">
         <v>35</v>
@@ -4310,13 +4323,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>741</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4330,16 +4343,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>742</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D44" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
@@ -4350,10 +4363,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>125</v>
+        <v>743</v>
       </c>
       <c r="D45">
         <v>110</v>
@@ -4364,10 +4377,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>744</v>
       </c>
       <c r="D46">
         <v>50</v>
@@ -4381,13 +4394,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>745</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D47">
         <v>70</v>
@@ -4395,13 +4408,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>746</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="D48">
         <v>90</v>
@@ -4412,19 +4425,20 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>747</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E1:M1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4444,7 +4458,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="9" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -4480,41 +4494,41 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>748</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>749</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>750</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -4525,13 +4539,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>751</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -4542,33 +4556,33 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>752</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>753</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="E8" s="2">
         <v>21</v>
@@ -4579,13 +4593,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>754</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="D9">
         <v>40</v>
@@ -4596,55 +4610,55 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>161</v>
+        <v>755</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>756</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>757</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>758</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>140</v>
@@ -4652,13 +4666,13 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>759</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>75</v>
@@ -4669,13 +4683,13 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>760</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="D15">
         <v>30</v>
@@ -4689,27 +4703,27 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>761</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>762</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="D17">
         <v>80</v>
@@ -4720,13 +4734,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>763</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="D18">
         <v>140</v>
@@ -4734,13 +4748,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>764</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="D19">
         <v>70</v>
@@ -4751,10 +4765,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>765</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -4765,13 +4779,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>194</v>
+        <v>766</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="D21">
         <v>70</v>
@@ -4779,27 +4793,27 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s">
-        <v>197</v>
+        <v>767</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>768</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="D23">
         <v>140</v>
@@ -4807,13 +4821,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>203</v>
+        <v>769</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -4824,30 +4838,30 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>206</v>
+        <v>770</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>771</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="E30" s="2">
         <v>70</v>
@@ -4855,13 +4869,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>772</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>214</v>
+        <v>146</v>
       </c>
       <c r="D31">
         <v>140</v>
@@ -4869,13 +4883,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>216</v>
+        <v>773</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4886,13 +4900,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>218</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>219</v>
+        <v>774</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D33">
         <v>70</v>
@@ -4900,13 +4914,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>775</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>223</v>
+        <v>152</v>
       </c>
       <c r="D34">
         <v>210</v>
@@ -4914,13 +4928,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s">
-        <v>225</v>
+        <v>776</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>226</v>
+        <v>154</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4928,13 +4942,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>228</v>
+        <v>777</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="D36">
         <v>50</v>
@@ -4945,13 +4959,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>778</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4965,13 +4979,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>779</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="D38">
         <v>90</v>
@@ -4982,27 +4996,27 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>780</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>238</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>239</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>781</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>241</v>
+        <v>164</v>
       </c>
       <c r="D40">
         <v>60</v>
@@ -5013,13 +5027,13 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>242</v>
+        <v>165</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>782</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="D41">
         <v>130</v>
@@ -5027,16 +5041,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>246</v>
+        <v>783</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2">
         <v>21</v>
@@ -5044,16 +5058,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>249</v>
+        <v>784</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="E43" s="2">
         <v>21</v>
@@ -5061,55 +5075,55 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="B44" t="s">
-        <v>252</v>
+        <v>785</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>786</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>257</v>
+        <v>175</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>787</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>259</v>
+        <v>176</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>260</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>261</v>
+        <v>788</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -5117,13 +5131,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>789</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5134,24 +5148,24 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>267</v>
+        <v>790</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>268</v>
+        <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>791</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -5164,6 +5178,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:M1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5184,7 +5199,7 @@
     <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="C1" s="1"/>
       <c r="D1" t="s">
-        <v>271</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5209,55 +5224,55 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>272</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>792</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="B4" t="s">
-        <v>276</v>
+        <v>793</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>277</v>
+        <v>188</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>278</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>794</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>277</v>
+        <v>188</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>281</v>
+        <v>795</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="D6">
         <v>90</v>
@@ -5268,13 +5283,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>796</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="D7">
         <v>140</v>
@@ -5282,27 +5297,27 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>287</v>
+        <v>797</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>288</v>
+        <v>195</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
-        <v>289</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
-        <v>290</v>
+        <v>798</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>291</v>
+        <v>197</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -5310,13 +5325,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
-        <v>292</v>
+        <v>198</v>
       </c>
       <c r="B10" t="s">
-        <v>293</v>
+        <v>799</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>294</v>
+        <v>199</v>
       </c>
       <c r="D10">
         <v>350</v>
@@ -5324,13 +5339,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>295</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>800</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>297</v>
+        <v>201</v>
       </c>
       <c r="D11">
         <v>280</v>
@@ -5338,13 +5353,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B12" t="s">
-        <v>299</v>
+        <v>801</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="D12">
         <v>140</v>
@@ -5352,13 +5367,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
-        <v>302</v>
+        <v>802</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>303</v>
+        <v>205</v>
       </c>
       <c r="D13">
         <v>350</v>
@@ -5366,16 +5381,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>305</v>
+        <v>803</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="E14" s="4">
         <v>63</v>
@@ -5383,27 +5398,27 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>307</v>
+        <v>208</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>804</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>309</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>805</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="D16">
         <v>170</v>
@@ -5411,27 +5426,27 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>806</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>315</v>
+        <v>213</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
+        <v>807</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>318</v>
+        <v>215</v>
       </c>
       <c r="D18">
         <v>60</v>
@@ -5442,13 +5457,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>319</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>320</v>
+        <v>808</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="D19">
         <v>40</v>
@@ -5459,13 +5474,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>322</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>323</v>
+        <v>809</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="D20">
         <v>140</v>
@@ -5476,16 +5491,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>326</v>
+        <v>810</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>327</v>
+        <v>221</v>
       </c>
       <c r="D21" t="s">
-        <v>328</v>
+        <v>222</v>
       </c>
       <c r="E21" s="4">
         <v>50</v>
@@ -5493,27 +5508,27 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="5" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>811</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>331</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s">
-        <v>332</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="5" t="s">
-        <v>333</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s">
-        <v>334</v>
+        <v>812</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>335</v>
+        <v>227</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -5524,13 +5539,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="5" t="s">
-        <v>336</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s">
-        <v>334</v>
+        <v>813</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>337</v>
+        <v>229</v>
       </c>
       <c r="F24" s="2">
         <v>90</v>
@@ -5538,13 +5553,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5" t="s">
-        <v>338</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s">
-        <v>339</v>
+        <v>814</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>340</v>
+        <v>231</v>
       </c>
       <c r="D27">
         <v>214</v>
@@ -5555,13 +5570,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5" t="s">
-        <v>341</v>
+        <v>232</v>
       </c>
       <c r="B28" t="s">
-        <v>342</v>
+        <v>815</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>343</v>
+        <v>233</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -5572,13 +5587,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5" t="s">
-        <v>344</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>345</v>
+        <v>816</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="D29">
         <v>280</v>
@@ -5586,27 +5601,27 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5" t="s">
-        <v>347</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s">
-        <v>348</v>
+        <v>817</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>349</v>
+        <v>237</v>
       </c>
       <c r="D30" t="s">
-        <v>350</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5" t="s">
-        <v>351</v>
+        <v>239</v>
       </c>
       <c r="B31" t="s">
-        <v>352</v>
+        <v>818</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>353</v>
+        <v>240</v>
       </c>
       <c r="D31">
         <v>170</v>
@@ -5614,13 +5629,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5" t="s">
-        <v>354</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s">
-        <v>355</v>
+        <v>819</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>356</v>
+        <v>242</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5631,27 +5646,27 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>357</v>
+        <v>243</v>
       </c>
       <c r="B33" t="s">
-        <v>358</v>
+        <v>820</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>359</v>
+        <v>244</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>360</v>
+        <v>245</v>
       </c>
       <c r="B34" t="s">
-        <v>361</v>
+        <v>821</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>362</v>
+        <v>246</v>
       </c>
       <c r="D34">
         <v>110</v>
@@ -5662,13 +5677,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="B35" t="s">
-        <v>364</v>
+        <v>822</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>253</v>
+        <v>172</v>
       </c>
       <c r="D35">
         <v>240</v>
@@ -5676,27 +5691,27 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="B36" t="s">
-        <v>366</v>
+        <v>823</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>367</v>
+        <v>249</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>368</v>
+        <v>250</v>
       </c>
       <c r="B37" t="s">
-        <v>369</v>
+        <v>824</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>370</v>
+        <v>251</v>
       </c>
       <c r="D37">
         <v>280</v>
@@ -5704,13 +5719,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>371</v>
+        <v>252</v>
       </c>
       <c r="B38" t="s">
-        <v>372</v>
+        <v>825</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>373</v>
+        <v>253</v>
       </c>
       <c r="D38">
         <v>65</v>
@@ -5721,13 +5736,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>374</v>
+        <v>254</v>
       </c>
       <c r="B39" t="s">
-        <v>375</v>
+        <v>826</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>376</v>
+        <v>255</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5735,41 +5750,41 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>377</v>
+        <v>256</v>
       </c>
       <c r="B40" t="s">
-        <v>378</v>
+        <v>827</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>379</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s">
-        <v>380</v>
+        <v>828</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>381</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>382</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>383</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>384</v>
+        <v>829</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>385</v>
+        <v>261</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5777,13 +5792,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>386</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s">
-        <v>387</v>
+        <v>830</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>388</v>
+        <v>263</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5791,13 +5806,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>389</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>390</v>
+        <v>831</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>391</v>
+        <v>265</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5808,41 +5823,41 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>392</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s">
-        <v>393</v>
+        <v>832</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>394</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>395</v>
+        <v>268</v>
       </c>
       <c r="B46" t="s">
-        <v>396</v>
+        <v>833</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>397</v>
+        <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>398</v>
+        <v>270</v>
       </c>
       <c r="B47" t="s">
-        <v>399</v>
+        <v>834</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>400</v>
+        <v>271</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -5852,6 +5867,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
@@ -5873,12 +5889,12 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>402</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5898,35 +5914,35 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>403</v>
+        <v>274</v>
       </c>
       <c r="G2" t="s">
-        <v>404</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>405</v>
+        <v>276</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>835</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>407</v>
+        <v>277</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>408</v>
+        <v>278</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>836</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>410</v>
+        <v>279</v>
       </c>
       <c r="D4">
         <v>280</v>
@@ -5934,13 +5950,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>837</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>413</v>
+        <v>281</v>
       </c>
       <c r="D5">
         <v>140</v>
@@ -5948,13 +5964,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>414</v>
+        <v>282</v>
       </c>
       <c r="B6" t="s">
-        <v>415</v>
+        <v>838</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>416</v>
+        <v>283</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -5965,13 +5981,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>417</v>
+        <v>284</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>839</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>419</v>
+        <v>285</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5982,13 +5998,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>421</v>
+        <v>840</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>422</v>
+        <v>287</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5999,13 +6015,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>288</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>841</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>425</v>
+        <v>289</v>
       </c>
       <c r="D9">
         <v>210</v>
@@ -6013,13 +6029,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>290</v>
       </c>
       <c r="B10" t="s">
-        <v>427</v>
+        <v>842</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>428</v>
+        <v>291</v>
       </c>
       <c r="D10">
         <v>140</v>
@@ -6027,27 +6043,27 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>429</v>
+        <v>292</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>843</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>431</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>432</v>
+        <v>294</v>
       </c>
       <c r="B12" t="s">
-        <v>433</v>
+        <v>844</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>434</v>
+        <v>295</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6058,27 +6074,27 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>435</v>
+        <v>296</v>
       </c>
       <c r="B13" t="s">
-        <v>436</v>
+        <v>845</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>437</v>
+        <v>297</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>438</v>
+        <v>298</v>
       </c>
       <c r="B14" t="s">
-        <v>439</v>
+        <v>846</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>440</v>
+        <v>299</v>
       </c>
       <c r="D14">
         <v>210</v>
@@ -6086,13 +6102,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>441</v>
+        <v>300</v>
       </c>
       <c r="B15" t="s">
-        <v>442</v>
+        <v>847</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="D15">
         <v>170</v>
@@ -6100,27 +6116,27 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>443</v>
+        <v>301</v>
       </c>
       <c r="B16" t="s">
-        <v>444</v>
+        <v>848</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>445</v>
+        <v>302</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>446</v>
+        <v>303</v>
       </c>
       <c r="B17" t="s">
-        <v>447</v>
+        <v>849</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>448</v>
+        <v>304</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6131,55 +6147,55 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>449</v>
+        <v>305</v>
       </c>
       <c r="B18" t="s">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>451</v>
+        <v>306</v>
       </c>
       <c r="D18" t="s">
-        <v>452</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>453</v>
+        <v>308</v>
       </c>
       <c r="B19" t="s">
-        <v>454</v>
+        <v>851</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>455</v>
+        <v>309</v>
       </c>
       <c r="D19" t="s">
-        <v>456</v>
+        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>457</v>
+        <v>311</v>
       </c>
       <c r="B20" t="s">
-        <v>458</v>
+        <v>852</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>459</v>
+        <v>312</v>
       </c>
       <c r="D20" t="s">
-        <v>460</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>461</v>
+        <v>314</v>
       </c>
       <c r="B21" t="s">
-        <v>462</v>
+        <v>853</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>463</v>
+        <v>315</v>
       </c>
       <c r="D21">
         <v>93</v>
@@ -6190,13 +6206,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>464</v>
+        <v>316</v>
       </c>
       <c r="B22" t="s">
-        <v>465</v>
+        <v>854</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>466</v>
+        <v>317</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6213,13 +6229,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>467</v>
+        <v>318</v>
       </c>
       <c r="B23" t="s">
-        <v>468</v>
+        <v>855</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>469</v>
+        <v>319</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6230,27 +6246,27 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>470</v>
+        <v>320</v>
       </c>
       <c r="B24" t="s">
-        <v>471</v>
+        <v>856</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>472</v>
+        <v>321</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>473</v>
+        <v>322</v>
       </c>
       <c r="B25" t="s">
-        <v>474</v>
+        <v>857</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>475</v>
+        <v>323</v>
       </c>
       <c r="D25">
         <v>350</v>
@@ -6258,13 +6274,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>476</v>
+        <v>324</v>
       </c>
       <c r="B26" t="s">
-        <v>477</v>
+        <v>858</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="D26">
         <v>210</v>
@@ -6272,13 +6288,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>479</v>
+        <v>326</v>
       </c>
       <c r="B27" t="s">
-        <v>480</v>
+        <v>859</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>481</v>
+        <v>327</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -6289,13 +6305,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>482</v>
+        <v>328</v>
       </c>
       <c r="B28" t="s">
-        <v>483</v>
+        <v>860</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>410</v>
+        <v>279</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -6306,13 +6322,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>484</v>
+        <v>329</v>
       </c>
       <c r="B29" t="s">
-        <v>334</v>
+        <v>861</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>485</v>
+        <v>330</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="2">
@@ -6321,10 +6337,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>486</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
-        <v>334</v>
+        <v>862</v>
       </c>
       <c r="F30" s="2">
         <v>65</v>
@@ -6332,16 +6348,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>487</v>
+        <v>332</v>
       </c>
       <c r="B32" t="s">
-        <v>488</v>
+        <v>863</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>489</v>
+        <v>333</v>
       </c>
       <c r="D32" t="s">
-        <v>490</v>
+        <v>334</v>
       </c>
       <c r="E32" s="4">
         <v>21</v>
@@ -6349,13 +6365,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>491</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s">
-        <v>492</v>
+        <v>864</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>70</v>
@@ -6363,13 +6379,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>493</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s">
-        <v>494</v>
+        <v>865</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>340</v>
+        <v>231</v>
       </c>
       <c r="D34">
         <v>214</v>
@@ -6380,13 +6396,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>495</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s">
-        <v>496</v>
+        <v>866</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>497</v>
+        <v>338</v>
       </c>
       <c r="D35">
         <v>210</v>
@@ -6394,13 +6410,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>498</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s">
-        <v>499</v>
+        <v>867</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="D36">
         <v>110</v>
@@ -6408,13 +6424,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>501</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
-        <v>502</v>
+        <v>868</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>425</v>
+        <v>289</v>
       </c>
       <c r="D37">
         <v>210</v>
@@ -6422,13 +6438,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>503</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s">
-        <v>504</v>
+        <v>869</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>505</v>
+        <v>343</v>
       </c>
       <c r="D38">
         <v>350</v>
@@ -6436,27 +6452,27 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>506</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s">
-        <v>507</v>
+        <v>870</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>508</v>
+        <v>345</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>509</v>
+        <v>346</v>
       </c>
       <c r="B40" t="s">
-        <v>510</v>
+        <v>871</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>511</v>
+        <v>347</v>
       </c>
       <c r="D40">
         <v>70</v>
@@ -6464,13 +6480,13 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>512</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s">
-        <v>513</v>
+        <v>872</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>514</v>
+        <v>349</v>
       </c>
       <c r="D41">
         <v>80</v>
@@ -6478,13 +6494,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>515</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>516</v>
+        <v>873</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>517</v>
+        <v>351</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6495,13 +6511,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>518</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s">
-        <v>519</v>
+        <v>874</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>520</v>
+        <v>353</v>
       </c>
       <c r="D43">
         <v>280</v>
@@ -6509,13 +6525,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>521</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s">
-        <v>522</v>
+        <v>875</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>523</v>
+        <v>355</v>
       </c>
       <c r="D44">
         <v>210</v>
@@ -6523,38 +6539,38 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>524</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s">
-        <v>525</v>
+        <v>876</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>526</v>
+        <v>357</v>
       </c>
       <c r="D45" t="s">
-        <v>332</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>527</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s">
-        <v>528</v>
+        <v>877</v>
       </c>
       <c r="D46" t="s">
-        <v>529</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>530</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s">
-        <v>531</v>
+        <v>878</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>532</v>
+        <v>361</v>
       </c>
       <c r="D47">
         <v>280</v>
@@ -6562,24 +6578,24 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>533</v>
+        <v>362</v>
       </c>
       <c r="B48" t="s">
-        <v>534</v>
+        <v>879</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>535</v>
+        <v>363</v>
       </c>
       <c r="B49" t="s">
-        <v>536</v>
+        <v>880</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>537</v>
+        <v>364</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -6590,13 +6606,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>538</v>
+        <v>365</v>
       </c>
       <c r="B50" t="s">
-        <v>539</v>
+        <v>881</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>540</v>
+        <v>366</v>
       </c>
       <c r="D50">
         <v>160</v>
@@ -6606,6 +6622,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6624,7 +6641,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="H1" s="1" t="s">
-        <v>541</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6644,18 +6661,18 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>542</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>543</v>
+        <v>369</v>
       </c>
       <c r="B3" t="s">
-        <v>544</v>
+        <v>882</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>545</v>
+        <v>370</v>
       </c>
       <c r="D3">
         <v>260</v>
@@ -6663,10 +6680,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>546</v>
+        <v>371</v>
       </c>
       <c r="B4" t="s">
-        <v>547</v>
+        <v>883</v>
       </c>
       <c r="D4">
         <v>130</v>
@@ -6677,13 +6694,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>548</v>
+        <v>372</v>
       </c>
       <c r="B5" t="s">
-        <v>549</v>
+        <v>884</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>550</v>
+        <v>373</v>
       </c>
       <c r="D5">
         <v>120</v>
@@ -6691,24 +6708,24 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>551</v>
+        <v>374</v>
       </c>
       <c r="B6" t="s">
-        <v>552</v>
+        <v>885</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>553</v>
+        <v>375</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>554</v>
+        <v>376</v>
       </c>
       <c r="B7" t="s">
-        <v>555</v>
+        <v>886</v>
       </c>
       <c r="D7">
         <v>148</v>
@@ -6716,10 +6733,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>556</v>
+        <v>377</v>
       </c>
       <c r="B8" t="s">
-        <v>557</v>
+        <v>887</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -6727,24 +6744,24 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>558</v>
+        <v>378</v>
       </c>
       <c r="B9" t="s">
-        <v>559</v>
+        <v>888</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>560</v>
+        <v>379</v>
       </c>
       <c r="D9" t="s">
-        <v>561</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>562</v>
+        <v>381</v>
       </c>
       <c r="B10" t="s">
-        <v>563</v>
+        <v>889</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -6755,13 +6772,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>564</v>
+        <v>382</v>
       </c>
       <c r="B11" t="s">
-        <v>565</v>
+        <v>890</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>566</v>
+        <v>383</v>
       </c>
       <c r="D11">
         <v>140</v>
@@ -6769,27 +6786,27 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>567</v>
+        <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>568</v>
+        <v>891</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>569</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>570</v>
+        <v>386</v>
       </c>
       <c r="B13" t="s">
-        <v>571</v>
+        <v>892</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>572</v>
+        <v>387</v>
       </c>
       <c r="E13" s="2">
         <v>21</v>
@@ -6797,35 +6814,35 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>573</v>
+        <v>388</v>
       </c>
       <c r="B14" t="s">
-        <v>574</v>
+        <v>893</v>
       </c>
       <c r="D14" t="s">
-        <v>575</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>576</v>
+        <v>390</v>
       </c>
       <c r="B15" t="s">
-        <v>577</v>
+        <v>894</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="B16" t="s">
-        <v>578</v>
+        <v>895</v>
       </c>
       <c r="D16">
         <v>210</v>
@@ -6833,27 +6850,27 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>579</v>
+        <v>391</v>
       </c>
       <c r="B17" t="s">
-        <v>580</v>
+        <v>896</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>581</v>
+        <v>392</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>582</v>
+        <v>393</v>
       </c>
       <c r="B18" t="s">
-        <v>583</v>
+        <v>897</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>584</v>
+        <v>394</v>
       </c>
       <c r="D18">
         <v>160</v>
@@ -6861,13 +6878,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>585</v>
+        <v>395</v>
       </c>
       <c r="B19" t="s">
-        <v>586</v>
+        <v>898</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>587</v>
+        <v>396</v>
       </c>
       <c r="D19">
         <v>340</v>
@@ -6875,35 +6892,35 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>588</v>
+        <v>397</v>
       </c>
       <c r="B20" t="s">
-        <v>589</v>
+        <v>899</v>
       </c>
       <c r="D20" t="s">
-        <v>590</v>
+        <v>398</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>591</v>
+        <v>399</v>
       </c>
       <c r="B21" t="s">
-        <v>592</v>
+        <v>900</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>593</v>
+        <v>400</v>
       </c>
       <c r="D21" t="s">
-        <v>594</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>595</v>
+        <v>402</v>
       </c>
       <c r="B22" t="s">
-        <v>596</v>
+        <v>901</v>
       </c>
       <c r="D22">
         <v>373</v>
@@ -6911,13 +6928,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>597</v>
+        <v>403</v>
       </c>
       <c r="B23" t="s">
-        <v>598</v>
+        <v>902</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>599</v>
+        <v>404</v>
       </c>
       <c r="D23">
         <v>145</v>
@@ -6928,10 +6945,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>600</v>
+        <v>405</v>
       </c>
       <c r="B24" t="s">
-        <v>601</v>
+        <v>903</v>
       </c>
       <c r="D24">
         <v>150</v>
@@ -6939,13 +6956,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>602</v>
+        <v>406</v>
       </c>
       <c r="B25" t="s">
-        <v>603</v>
+        <v>904</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>604</v>
+        <v>407</v>
       </c>
       <c r="D25">
         <v>250</v>
@@ -6953,13 +6970,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>605</v>
+        <v>408</v>
       </c>
       <c r="B26" t="s">
-        <v>606</v>
+        <v>905</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>607</v>
+        <v>409</v>
       </c>
       <c r="D26">
         <v>70</v>
@@ -6970,27 +6987,27 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>608</v>
+        <v>410</v>
       </c>
       <c r="B27" t="s">
-        <v>609</v>
+        <v>906</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>610</v>
+        <v>411</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>611</v>
+        <v>412</v>
       </c>
       <c r="B28" t="s">
-        <v>612</v>
+        <v>907</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>610</v>
+        <v>411</v>
       </c>
       <c r="D28">
         <v>420</v>
@@ -6998,13 +7015,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>613</v>
+        <v>413</v>
       </c>
       <c r="B29" t="s">
-        <v>614</v>
+        <v>908</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>615</v>
+        <v>414</v>
       </c>
       <c r="D29">
         <v>140</v>
@@ -7012,30 +7029,30 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>616</v>
+        <v>415</v>
       </c>
       <c r="B30" t="s">
-        <v>617</v>
+        <v>909</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>618</v>
+        <v>416</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>619</v>
+        <v>417</v>
       </c>
       <c r="B34" t="s">
-        <v>620</v>
+        <v>910</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>621</v>
+        <v>418</v>
       </c>
       <c r="D34">
         <v>140</v>
@@ -7043,13 +7060,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>622</v>
+        <v>419</v>
       </c>
       <c r="B35" t="s">
-        <v>623</v>
+        <v>911</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D35">
         <v>50</v>
@@ -7060,13 +7077,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>624</v>
+        <v>420</v>
       </c>
       <c r="B36" t="s">
-        <v>625</v>
+        <v>912</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>626</v>
+        <v>421</v>
       </c>
       <c r="D36">
         <v>552</v>
@@ -7077,13 +7094,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>627</v>
+        <v>422</v>
       </c>
       <c r="B37" t="s">
-        <v>628</v>
+        <v>913</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>629</v>
+        <v>423</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7097,13 +7114,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>630</v>
+        <v>424</v>
       </c>
       <c r="B38" t="s">
-        <v>631</v>
+        <v>914</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>632</v>
+        <v>425</v>
       </c>
       <c r="D38">
         <v>210</v>
@@ -7111,13 +7128,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>633</v>
+        <v>426</v>
       </c>
       <c r="B39" t="s">
-        <v>634</v>
+        <v>915</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>632</v>
+        <v>425</v>
       </c>
       <c r="D39">
         <v>50</v>
@@ -7128,13 +7145,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>635</v>
+        <v>427</v>
       </c>
       <c r="B40" t="s">
-        <v>636</v>
+        <v>916</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>637</v>
+        <v>428</v>
       </c>
       <c r="D40">
         <v>175</v>
@@ -7142,27 +7159,27 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>638</v>
+        <v>429</v>
       </c>
       <c r="B41" t="s">
-        <v>639</v>
+        <v>917</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>640</v>
+        <v>430</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>641</v>
+        <v>431</v>
       </c>
       <c r="B42" t="s">
-        <v>642</v>
+        <v>918</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>643</v>
+        <v>432</v>
       </c>
       <c r="D42">
         <v>210</v>
@@ -7170,13 +7187,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>644</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s">
-        <v>645</v>
+        <v>919</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>646</v>
+        <v>434</v>
       </c>
       <c r="D43">
         <v>100</v>
@@ -7187,27 +7204,27 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>647</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s">
-        <v>648</v>
+        <v>920</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>300</v>
+        <v>203</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>649</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s">
-        <v>650</v>
+        <v>921</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>651</v>
+        <v>437</v>
       </c>
       <c r="D45">
         <v>380</v>
@@ -7215,27 +7232,27 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>652</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s">
-        <v>653</v>
+        <v>922</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>654</v>
+        <v>439</v>
       </c>
       <c r="D46" t="s">
-        <v>655</v>
+        <v>440</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>656</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s">
-        <v>657</v>
+        <v>923</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="D47">
         <v>214</v>
@@ -7246,10 +7263,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>658</v>
+        <v>442</v>
       </c>
       <c r="B48" t="s">
-        <v>659</v>
+        <v>924</v>
       </c>
       <c r="D48">
         <v>490</v>
@@ -7257,13 +7274,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>660</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s">
-        <v>661</v>
+        <v>925</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>662</v>
+        <v>444</v>
       </c>
       <c r="D49">
         <v>490</v>
@@ -7271,10 +7288,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>663</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s">
-        <v>664</v>
+        <v>926</v>
       </c>
       <c r="D50">
         <v>34</v>
@@ -7285,38 +7302,38 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>665</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s">
-        <v>666</v>
+        <v>927</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>667</v>
+        <v>447</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>668</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s">
-        <v>669</v>
+        <v>928</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>670</v>
+        <v>449</v>
       </c>
       <c r="D52" t="s">
-        <v>671</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>672</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s">
-        <v>673</v>
+        <v>929</v>
       </c>
       <c r="D53">
         <v>140</v>
@@ -7324,13 +7341,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>674</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s">
-        <v>675</v>
+        <v>930</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>676</v>
+        <v>453</v>
       </c>
       <c r="D54">
         <v>10</v>
@@ -7341,10 +7358,11 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7365,7 +7383,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="H1" s="1" t="s">
-        <v>677</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7388,21 +7406,21 @@
         <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>678</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>679</v>
+        <v>456</v>
       </c>
       <c r="B3" t="s">
-        <v>680</v>
+        <v>931</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>681</v>
+        <v>457</v>
       </c>
       <c r="D3" t="s">
-        <v>682</v>
+        <v>458</v>
       </c>
       <c r="E3" s="2">
         <v>21</v>
@@ -7413,13 +7431,13 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>683</v>
+        <v>459</v>
       </c>
       <c r="B4" t="s">
-        <v>684</v>
+        <v>932</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>685</v>
+        <v>460</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -7430,13 +7448,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>686</v>
+        <v>461</v>
       </c>
       <c r="B5" t="s">
-        <v>687</v>
+        <v>933</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>688</v>
+        <v>462</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7447,13 +7465,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>689</v>
+        <v>463</v>
       </c>
       <c r="B6" t="s">
-        <v>690</v>
+        <v>934</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>691</v>
+        <v>464</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -7464,13 +7482,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>692</v>
+        <v>465</v>
       </c>
       <c r="B7" t="s">
-        <v>693</v>
+        <v>935</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>694</v>
+        <v>466</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -7484,30 +7502,30 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>695</v>
+        <v>467</v>
       </c>
       <c r="B8" t="s">
-        <v>696</v>
+        <v>936</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>697</v>
+        <v>468</v>
       </c>
       <c r="D8">
         <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="B9" t="s">
-        <v>699</v>
+        <v>937</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>700</v>
+        <v>470</v>
       </c>
       <c r="D9">
         <v>22</v>
@@ -7518,10 +7536,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>701</v>
+        <v>471</v>
       </c>
       <c r="B10" t="s">
-        <v>702</v>
+        <v>938</v>
       </c>
       <c r="D10">
         <v>230</v>
@@ -7532,13 +7550,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>703</v>
+        <v>472</v>
       </c>
       <c r="B11" t="s">
-        <v>704</v>
+        <v>939</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>170</v>
@@ -7546,10 +7564,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>705</v>
+        <v>473</v>
       </c>
       <c r="B12" t="s">
-        <v>706</v>
+        <v>940</v>
       </c>
       <c r="D12">
         <v>190</v>
@@ -7557,16 +7575,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>707</v>
+        <v>474</v>
       </c>
       <c r="B13" t="s">
-        <v>708</v>
+        <v>941</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>709</v>
+        <v>475</v>
       </c>
       <c r="D13" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2">
         <v>21</v>
@@ -7574,10 +7592,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>710</v>
+        <v>476</v>
       </c>
       <c r="B14" t="s">
-        <v>711</v>
+        <v>942</v>
       </c>
       <c r="D14">
         <v>140</v>
@@ -7585,10 +7603,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>712</v>
+        <v>477</v>
       </c>
       <c r="B15" t="s">
-        <v>713</v>
+        <v>943</v>
       </c>
       <c r="D15">
         <v>250</v>
@@ -7596,27 +7614,27 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>714</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>715</v>
+        <v>944</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>716</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>717</v>
+        <v>480</v>
       </c>
       <c r="B17" t="s">
-        <v>718</v>
+        <v>945</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>719</v>
+        <v>481</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7627,52 +7645,52 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>720</v>
+        <v>482</v>
       </c>
       <c r="B18" t="s">
-        <v>721</v>
+        <v>946</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>722</v>
+        <v>483</v>
       </c>
       <c r="D18" t="s">
-        <v>723</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>724</v>
+        <v>485</v>
       </c>
       <c r="B19" t="s">
-        <v>725</v>
+        <v>947</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>726</v>
+        <v>486</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>727</v>
+        <v>487</v>
       </c>
       <c r="B20" t="s">
-        <v>728</v>
+        <v>948</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>729</v>
+        <v>488</v>
       </c>
       <c r="B21" t="s">
-        <v>730</v>
+        <v>949</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>731</v>
+        <v>489</v>
       </c>
       <c r="D21">
         <v>210</v>
@@ -7683,13 +7701,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>732</v>
+        <v>490</v>
       </c>
       <c r="B22" t="s">
-        <v>733</v>
+        <v>950</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>734</v>
+        <v>491</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7700,16 +7718,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>735</v>
+        <v>492</v>
       </c>
       <c r="B23" t="s">
-        <v>736</v>
+        <v>951</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>737</v>
+        <v>493</v>
       </c>
       <c r="D23" t="s">
-        <v>738</v>
+        <v>494</v>
       </c>
       <c r="E23" s="2">
         <v>21</v>
@@ -7720,13 +7738,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>739</v>
+        <v>495</v>
       </c>
       <c r="B24" t="s">
-        <v>740</v>
+        <v>952</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>741</v>
+        <v>496</v>
       </c>
       <c r="D24">
         <v>280</v>
@@ -7734,13 +7752,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>742</v>
+        <v>497</v>
       </c>
       <c r="B25" t="s">
-        <v>743</v>
+        <v>953</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>744</v>
+        <v>498</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7751,13 +7769,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>745</v>
+        <v>499</v>
       </c>
       <c r="B26" t="s">
-        <v>746</v>
+        <v>954</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>353</v>
+        <v>240</v>
       </c>
       <c r="D26">
         <v>140</v>
@@ -7765,27 +7783,27 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>747</v>
+        <v>500</v>
       </c>
       <c r="B31" t="s">
-        <v>748</v>
+        <v>501</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>749</v>
+        <v>502</v>
       </c>
       <c r="B32" t="s">
-        <v>750</v>
+        <v>503</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>751</v>
+        <v>504</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7799,16 +7817,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>752</v>
+        <v>505</v>
       </c>
       <c r="B33" t="s">
-        <v>753</v>
+        <v>506</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
       <c r="D33" t="s">
-        <v>755</v>
+        <v>508</v>
       </c>
       <c r="E33">
         <v>-9</v>
@@ -7816,13 +7834,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>756</v>
+        <v>509</v>
       </c>
       <c r="B34" t="s">
-        <v>757</v>
+        <v>510</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>758</v>
+        <v>511</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7836,10 +7854,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>759</v>
+        <v>512</v>
       </c>
       <c r="B35" t="s">
-        <v>760</v>
+        <v>513</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -7850,10 +7868,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>761</v>
+        <v>514</v>
       </c>
       <c r="B36" t="s">
-        <v>762</v>
+        <v>515</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7867,13 +7885,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>763</v>
+        <v>516</v>
       </c>
       <c r="B37" t="s">
-        <v>764</v>
+        <v>517</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>391</v>
+        <v>265</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7884,10 +7902,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>765</v>
+        <v>518</v>
       </c>
       <c r="B38" t="s">
-        <v>766</v>
+        <v>519</v>
       </c>
       <c r="D38">
         <v>150</v>
@@ -7898,13 +7916,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>767</v>
+        <v>520</v>
       </c>
       <c r="B39" t="s">
-        <v>768</v>
+        <v>521</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>769</v>
+        <v>522</v>
       </c>
       <c r="D39">
         <v>270</v>
@@ -7912,24 +7930,24 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>770</v>
+        <v>523</v>
       </c>
       <c r="B40" t="s">
-        <v>771</v>
+        <v>524</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>772</v>
+        <v>525</v>
       </c>
       <c r="B41" t="s">
-        <v>773</v>
+        <v>526</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>774</v>
+        <v>527</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -7943,24 +7961,24 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>775</v>
+        <v>528</v>
       </c>
       <c r="B42" t="s">
-        <v>776</v>
+        <v>529</v>
       </c>
       <c r="D42" t="s">
-        <v>529</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>777</v>
+        <v>530</v>
       </c>
       <c r="B43" t="s">
-        <v>778</v>
+        <v>531</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>779</v>
+        <v>532</v>
       </c>
       <c r="D43">
         <v>45</v>
@@ -7971,13 +7989,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>780</v>
+        <v>533</v>
       </c>
       <c r="B44" t="s">
-        <v>781</v>
+        <v>534</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>782</v>
+        <v>535</v>
       </c>
       <c r="D44">
         <v>350</v>
@@ -7985,10 +8003,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>783</v>
+        <v>536</v>
       </c>
       <c r="B45" t="s">
-        <v>784</v>
+        <v>537</v>
       </c>
       <c r="D45">
         <v>210</v>
@@ -7999,13 +8017,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>785</v>
+        <v>538</v>
       </c>
       <c r="B46" t="s">
-        <v>786</v>
+        <v>539</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>787</v>
+        <v>540</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -8016,13 +8034,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>788</v>
+        <v>541</v>
       </c>
       <c r="B47" t="s">
-        <v>789</v>
+        <v>542</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>790</v>
+        <v>543</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -8033,13 +8051,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>791</v>
+        <v>544</v>
       </c>
       <c r="B48" t="s">
-        <v>792</v>
+        <v>545</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>793</v>
+        <v>546</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -8050,13 +8068,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>794</v>
+        <v>547</v>
       </c>
       <c r="B49" t="s">
-        <v>795</v>
+        <v>548</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>796</v>
+        <v>549</v>
       </c>
       <c r="D49">
         <v>70</v>
@@ -8064,13 +8082,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>797</v>
+        <v>550</v>
       </c>
       <c r="B50" t="s">
-        <v>798</v>
+        <v>551</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>799</v>
+        <v>552</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -8084,13 +8102,13 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>800</v>
+        <v>553</v>
       </c>
       <c r="B51" t="s">
-        <v>801</v>
+        <v>554</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>802</v>
+        <v>555</v>
       </c>
       <c r="D51">
         <v>70</v>
@@ -8098,16 +8116,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>803</v>
+        <v>556</v>
       </c>
       <c r="B52" t="s">
-        <v>804</v>
+        <v>557</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>805</v>
+        <v>558</v>
       </c>
       <c r="D52" t="s">
-        <v>806</v>
+        <v>559</v>
       </c>
       <c r="E52" s="2">
         <v>47</v>
@@ -8115,13 +8133,13 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>807</v>
+        <v>560</v>
       </c>
       <c r="B53" t="s">
-        <v>808</v>
+        <v>561</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>809</v>
+        <v>562</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -8131,6 +8149,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8150,7 +8169,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="C1" s="1" t="s">
-        <v>810</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8172,13 +8191,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>811</v>
+        <v>564</v>
       </c>
       <c r="B3" t="s">
-        <v>812</v>
+        <v>955</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>813</v>
+        <v>565</v>
       </c>
       <c r="D3">
         <v>350</v>
@@ -8186,52 +8205,52 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>814</v>
+        <v>566</v>
       </c>
       <c r="B4" t="s">
-        <v>815</v>
+        <v>956</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>816</v>
+        <v>567</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>817</v>
+        <v>568</v>
       </c>
       <c r="B5" t="s">
-        <v>818</v>
+        <v>957</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>819</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>820</v>
+        <v>570</v>
       </c>
       <c r="B6" t="s">
-        <v>821</v>
+        <v>958</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>822</v>
+        <v>571</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>823</v>
+        <v>572</v>
       </c>
       <c r="B7" t="s">
-        <v>824</v>
+        <v>959</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>825</v>
+        <v>573</v>
       </c>
       <c r="D7">
         <v>164</v>
@@ -8239,55 +8258,55 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>826</v>
+        <v>574</v>
       </c>
       <c r="B8" t="s">
-        <v>827</v>
+        <v>960</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>828</v>
+        <v>575</v>
       </c>
       <c r="B9" t="s">
-        <v>829</v>
+        <v>961</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>830</v>
+        <v>576</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>831</v>
+        <v>577</v>
       </c>
       <c r="B10" t="s">
-        <v>832</v>
+        <v>962</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>833</v>
+        <v>578</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>834</v>
+        <v>579</v>
       </c>
       <c r="B11" t="s">
-        <v>835</v>
+        <v>963</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>836</v>
+        <v>580</v>
       </c>
       <c r="D11">
         <v>210</v>
@@ -8295,13 +8314,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>837</v>
+        <v>581</v>
       </c>
       <c r="B12" t="s">
-        <v>838</v>
+        <v>964</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>839</v>
+        <v>582</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8312,13 +8331,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>840</v>
+        <v>583</v>
       </c>
       <c r="B13" t="s">
-        <v>841</v>
+        <v>965</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>842</v>
+        <v>584</v>
       </c>
       <c r="D13">
         <v>90</v>
@@ -8329,13 +8348,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>843</v>
+        <v>585</v>
       </c>
       <c r="B14" t="s">
-        <v>844</v>
+        <v>966</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -8346,13 +8365,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>845</v>
+        <v>586</v>
       </c>
       <c r="B20" t="s">
-        <v>846</v>
+        <v>967</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>847</v>
+        <v>587</v>
       </c>
       <c r="D20">
         <v>210</v>
@@ -8360,13 +8379,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>848</v>
+        <v>588</v>
       </c>
       <c r="B21" t="s">
-        <v>849</v>
+        <v>968</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>850</v>
+        <v>589</v>
       </c>
       <c r="D21">
         <v>270</v>
@@ -8374,13 +8393,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>851</v>
+        <v>590</v>
       </c>
       <c r="B22" t="s">
-        <v>852</v>
+        <v>969</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>853</v>
+        <v>591</v>
       </c>
       <c r="D22">
         <v>350</v>
@@ -8388,41 +8407,41 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>854</v>
+        <v>592</v>
       </c>
       <c r="B23" t="s">
-        <v>855</v>
+        <v>970</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>856</v>
+        <v>593</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>857</v>
+        <v>594</v>
       </c>
       <c r="B24" t="s">
-        <v>858</v>
+        <v>971</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>859</v>
+        <v>595</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>860</v>
+        <v>596</v>
       </c>
       <c r="B25" t="s">
-        <v>861</v>
+        <v>972</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>862</v>
+        <v>597</v>
       </c>
       <c r="D25">
         <v>140</v>
@@ -8433,13 +8452,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>863</v>
+        <v>598</v>
       </c>
       <c r="B26" t="s">
-        <v>864</v>
+        <v>973</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>865</v>
+        <v>599</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8450,13 +8469,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>866</v>
+        <v>600</v>
       </c>
       <c r="B27" t="s">
-        <v>867</v>
+        <v>974</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>868</v>
+        <v>601</v>
       </c>
       <c r="D27">
         <v>420</v>
@@ -8464,13 +8483,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>869</v>
+        <v>602</v>
       </c>
       <c r="B28" t="s">
-        <v>870</v>
+        <v>975</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>643</v>
+        <v>432</v>
       </c>
       <c r="D28">
         <v>490</v>
@@ -8478,13 +8497,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>871</v>
+        <v>603</v>
       </c>
       <c r="B29" t="s">
-        <v>872</v>
+        <v>976</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>873</v>
+        <v>604</v>
       </c>
       <c r="D29">
         <v>70</v>
@@ -8495,66 +8514,66 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>874</v>
+        <v>605</v>
       </c>
       <c r="B30" t="s">
-        <v>875</v>
+        <v>977</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>876</v>
+        <v>606</v>
       </c>
       <c r="D30" t="s">
-        <v>401</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>877</v>
+        <v>607</v>
       </c>
       <c r="B31" t="s">
-        <v>878</v>
+        <v>978</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>859</v>
+        <v>595</v>
       </c>
       <c r="D31" t="s">
-        <v>879</v>
+        <v>608</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>880</v>
+        <v>609</v>
       </c>
       <c r="B32" t="s">
-        <v>881</v>
+        <v>979</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>882</v>
+        <v>610</v>
       </c>
       <c r="B33" t="s">
-        <v>883</v>
+        <v>980</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>884</v>
+        <v>611</v>
       </c>
       <c r="D33" t="s">
-        <v>885</v>
+        <v>612</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>886</v>
+        <v>613</v>
       </c>
       <c r="B34" t="s">
-        <v>887</v>
+        <v>981</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>448</v>
+        <v>304</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8565,27 +8584,27 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>888</v>
+        <v>614</v>
       </c>
       <c r="B35" t="s">
-        <v>889</v>
+        <v>982</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>890</v>
+        <v>615</v>
       </c>
       <c r="B36" t="s">
-        <v>891</v>
+        <v>983</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>892</v>
+        <v>616</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -8593,13 +8612,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>893</v>
+        <v>617</v>
       </c>
       <c r="B37" t="s">
-        <v>894</v>
+        <v>984</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>895</v>
+        <v>618</v>
       </c>
       <c r="D37">
         <v>140</v>
@@ -8607,27 +8626,27 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>896</v>
+        <v>619</v>
       </c>
       <c r="B38" t="s">
-        <v>897</v>
+        <v>985</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>898</v>
+        <v>620</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>899</v>
+        <v>621</v>
       </c>
       <c r="B39" t="s">
-        <v>900</v>
+        <v>986</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>587</v>
+        <v>396</v>
       </c>
       <c r="D39">
         <v>420</v>
@@ -8635,13 +8654,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>901</v>
+        <v>622</v>
       </c>
       <c r="B40" t="s">
-        <v>902</v>
+        <v>987</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>903</v>
+        <v>623</v>
       </c>
       <c r="D40">
         <v>110</v>
@@ -8649,10 +8668,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>904</v>
+        <v>624</v>
       </c>
       <c r="B41" t="s">
-        <v>905</v>
+        <v>988</v>
       </c>
       <c r="D41">
         <v>180</v>
@@ -8660,13 +8679,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>906</v>
+        <v>625</v>
       </c>
       <c r="B42" t="s">
-        <v>907</v>
+        <v>989</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>908</v>
+        <v>626</v>
       </c>
       <c r="D42">
         <v>420</v>
@@ -8674,13 +8693,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>909</v>
+        <v>627</v>
       </c>
       <c r="B43" t="s">
-        <v>910</v>
+        <v>990</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>911</v>
+        <v>628</v>
       </c>
       <c r="D43">
         <v>70</v>
@@ -8688,13 +8707,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>912</v>
+        <v>629</v>
       </c>
       <c r="B44" t="s">
-        <v>913</v>
+        <v>991</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="D44">
         <v>280</v>
@@ -8702,19 +8721,20 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>914</v>
+        <v>630</v>
       </c>
       <c r="B45" t="s">
-        <v>915</v>
+        <v>992</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>497</v>
+        <v>338</v>
       </c>
       <c r="D45">
         <v>210</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8734,7 +8754,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="F1" s="1" t="s">
-        <v>916</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8756,27 +8776,27 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>917</v>
+        <v>632</v>
       </c>
       <c r="B3" t="s">
-        <v>918</v>
+        <v>993</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>919</v>
+        <v>633</v>
       </c>
       <c r="D3" t="s">
-        <v>920</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>921</v>
+        <v>635</v>
       </c>
       <c r="B4" t="s">
-        <v>922</v>
+        <v>994</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>923</v>
+        <v>636</v>
       </c>
       <c r="D4">
         <v>70</v>
@@ -8787,69 +8807,69 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>924</v>
+        <v>637</v>
       </c>
       <c r="B5" t="s">
-        <v>925</v>
+        <v>995</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>926</v>
+        <v>638</v>
       </c>
       <c r="D5" t="s">
-        <v>927</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>928</v>
+        <v>640</v>
       </c>
       <c r="B6" t="s">
-        <v>929</v>
+        <v>996</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>419</v>
+        <v>285</v>
       </c>
       <c r="D6" t="s">
-        <v>927</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>930</v>
+        <v>641</v>
       </c>
       <c r="B7" t="s">
-        <v>931</v>
+        <v>997</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>932</v>
+        <v>642</v>
       </c>
       <c r="B8" t="s">
-        <v>933</v>
+        <v>998</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>934</v>
+        <v>643</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>935</v>
+        <v>644</v>
       </c>
       <c r="B9" t="s">
-        <v>936</v>
+        <v>999</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>937</v>
+        <v>645</v>
       </c>
       <c r="D9">
         <v>200</v>
@@ -8857,13 +8877,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>938</v>
+        <v>646</v>
       </c>
       <c r="B10" t="s">
-        <v>939</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>691</v>
+        <v>464</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -8871,13 +8891,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>940</v>
+        <v>647</v>
       </c>
       <c r="B11" t="s">
-        <v>941</v>
+        <v>1001</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>942</v>
+        <v>648</v>
       </c>
       <c r="D11">
         <v>30</v>
@@ -8888,10 +8908,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>943</v>
+        <v>649</v>
       </c>
       <c r="B12" t="s">
-        <v>944</v>
+        <v>1002</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8902,27 +8922,27 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>945</v>
+        <v>650</v>
       </c>
       <c r="B13" t="s">
-        <v>946</v>
+        <v>1003</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>947</v>
+        <v>651</v>
       </c>
       <c r="D13" t="s">
-        <v>927</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>948</v>
+        <v>652</v>
       </c>
       <c r="B14" t="s">
-        <v>949</v>
+        <v>1004</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>950</v>
+        <v>653</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -8933,27 +8953,27 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>951</v>
+        <v>654</v>
       </c>
       <c r="B15" t="s">
-        <v>952</v>
+        <v>1005</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>927</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>953</v>
+        <v>655</v>
       </c>
       <c r="B16" t="s">
-        <v>954</v>
+        <v>1006</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>955</v>
+        <v>656</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -8964,16 +8984,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>956</v>
+        <v>657</v>
       </c>
       <c r="B17" t="s">
-        <v>957</v>
+        <v>1007</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>958</v>
+        <v>658</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2">
         <v>21</v>
@@ -8981,58 +9001,58 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>959</v>
+        <v>659</v>
       </c>
       <c r="B18" t="s">
-        <v>960</v>
+        <v>1008</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>961</v>
+        <v>660</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>962</v>
+        <v>661</v>
       </c>
       <c r="B19" t="s">
-        <v>963</v>
+        <v>1009</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>964</v>
+        <v>662</v>
       </c>
       <c r="D19" t="s">
-        <v>965</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>966</v>
+        <v>664</v>
       </c>
       <c r="B20" t="s">
-        <v>967</v>
+        <v>1010</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>968</v>
+        <v>665</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>969</v>
+        <v>666</v>
       </c>
       <c r="B21" t="s">
-        <v>970</v>
+        <v>1011</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>971</v>
+        <v>667</v>
       </c>
       <c r="D21" t="s">
-        <v>972</v>
+        <v>668</v>
       </c>
       <c r="E21" s="2">
         <v>10</v>
@@ -9040,27 +9060,27 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>973</v>
+        <v>669</v>
       </c>
       <c r="B22" t="s">
-        <v>974</v>
+        <v>1012</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>975</v>
+        <v>670</v>
       </c>
       <c r="D22" t="s">
-        <v>976</v>
+        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>977</v>
+        <v>672</v>
       </c>
       <c r="B23" t="s">
-        <v>978</v>
+        <v>1013</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>265</v>
+        <v>180</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -9071,13 +9091,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>979</v>
+        <v>673</v>
       </c>
       <c r="B24" t="s">
-        <v>980</v>
+        <v>1014</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>981</v>
+        <v>674</v>
       </c>
       <c r="D24">
         <v>230</v>
@@ -9085,13 +9105,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>982</v>
+        <v>675</v>
       </c>
       <c r="B28" t="s">
-        <v>983</v>
+        <v>1015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>984</v>
+        <v>676</v>
       </c>
       <c r="D28">
         <v>90</v>
@@ -9099,16 +9119,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>985</v>
+        <v>677</v>
       </c>
       <c r="B29" t="s">
-        <v>986</v>
+        <v>1016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>926</v>
+        <v>638</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="E29" s="2">
         <v>21</v>
@@ -9116,13 +9136,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>987</v>
+        <v>678</v>
       </c>
       <c r="B30" t="s">
-        <v>988</v>
+        <v>1017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>989</v>
+        <v>679</v>
       </c>
       <c r="D30">
         <v>410</v>
@@ -9133,27 +9153,27 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>990</v>
+        <v>680</v>
       </c>
       <c r="B31" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>667</v>
+        <v>447</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>992</v>
+        <v>681</v>
       </c>
       <c r="B32" t="s">
-        <v>993</v>
+        <v>1019</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>994</v>
+        <v>682</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -9161,13 +9181,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>995</v>
+        <v>683</v>
       </c>
       <c r="B33" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>997</v>
+        <v>684</v>
       </c>
       <c r="D33">
         <v>140</v>
@@ -9175,13 +9195,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>998</v>
+        <v>685</v>
       </c>
       <c r="B34" t="s">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1000</v>
+        <v>686</v>
       </c>
       <c r="D34">
         <v>210</v>
@@ -9192,13 +9212,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>1001</v>
+        <v>687</v>
       </c>
       <c r="B35" t="s">
-        <v>1002</v>
+        <v>1022</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1003</v>
+        <v>688</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -9209,13 +9229,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>1004</v>
+        <v>689</v>
       </c>
       <c r="B36" t="s">
-        <v>1005</v>
+        <v>1023</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1006</v>
+        <v>690</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -9226,27 +9246,27 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>1007</v>
+        <v>691</v>
       </c>
       <c r="B37" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>621</v>
+        <v>418</v>
       </c>
       <c r="D37" t="s">
-        <v>1009</v>
+        <v>692</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>1010</v>
+        <v>693</v>
       </c>
       <c r="B38" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1012</v>
+        <v>694</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -9254,13 +9274,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>1013</v>
+        <v>695</v>
       </c>
       <c r="B39" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1015</v>
+        <v>696</v>
       </c>
       <c r="D39">
         <v>350</v>
@@ -9268,13 +9288,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>1016</v>
+        <v>697</v>
       </c>
       <c r="B40" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1018</v>
+        <v>698</v>
       </c>
       <c r="D40">
         <v>210</v>
@@ -9282,13 +9302,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>1019</v>
+        <v>699</v>
       </c>
       <c r="B41" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>1021</v>
+        <v>700</v>
       </c>
       <c r="D41">
         <v>138</v>
@@ -9296,13 +9316,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>1022</v>
+        <v>701</v>
       </c>
       <c r="B42" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>1024</v>
+        <v>702</v>
       </c>
       <c r="D42">
         <v>210</v>
@@ -9310,10 +9330,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>1025</v>
+        <v>703</v>
       </c>
       <c r="B43" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D43">
         <v>210</v>
@@ -9321,16 +9341,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>1027</v>
+        <v>704</v>
       </c>
       <c r="B44" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>356</v>
+        <v>242</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2">
         <v>21</v>
@@ -9340,6 +9360,7 @@
       <c r="E45" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/FEES REGISTER 20251.xlsx
+++ b/public/FEES REGISTER 20251.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fau\Desktop\Websites\detema_sec\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E90B96-DFFC-4804-A0C7-AA5EF08DBD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F852B1CE-CEDE-4A98-9984-4B2170E5F6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Form 1 East" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="1029">
   <si>
     <t>FORM 1 EAST FEES REGISTER</t>
   </si>
@@ -58,9 +58,6 @@
     <t>TERM 3</t>
   </si>
   <si>
-    <t>2026 term1</t>
-  </si>
-  <si>
     <t>DUBE AMANDA D</t>
   </si>
   <si>
@@ -865,9 +862,6 @@
     <t>TERM 1 2026</t>
   </si>
   <si>
-    <t>BALANCE</t>
-  </si>
-  <si>
     <t>DUBE BEAUTY S</t>
   </si>
   <si>
@@ -1144,9 +1138,6 @@
     <t>FORM 3 SOUTH FEES REGISTER</t>
   </si>
   <si>
-    <t>2026 term 1</t>
-  </si>
-  <si>
     <t>CHITUMBURA PALESA V</t>
   </si>
   <si>
@@ -1405,9 +1396,6 @@
     <t>FORM 3 NORTH FEES REGISTER</t>
   </si>
   <si>
-    <t>2026 TERM1</t>
-  </si>
-  <si>
     <t>BANDURE HENRIETTA A</t>
   </si>
   <si>
@@ -3134,6 +3122,9 @@
   </si>
   <si>
     <t>DET-2022-077</t>
+  </si>
+  <si>
+    <t>TERM 3 2025</t>
   </si>
 </sst>
 </file>
@@ -3751,21 +3742,21 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>705</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3776,13 +3767,13 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>702</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>706</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -3793,27 +3784,27 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>703</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>707</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>704</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>708</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="D6">
         <v>140</v>
@@ -3821,41 +3812,41 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>705</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
-        <v>709</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>706</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="s">
-        <v>710</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>707</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>711</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -3863,16 +3854,16 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>708</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>712</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" t="s">
         <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
       </c>
       <c r="E10" s="2">
         <v>21</v>
@@ -3880,13 +3871,13 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>709</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>713</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3894,13 +3885,13 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>710</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>714</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3911,13 +3902,13 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>711</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="B13" t="s">
-        <v>715</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>30</v>
       </c>
       <c r="D13">
         <v>40</v>
@@ -3928,27 +3919,27 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>712</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B14" t="s">
-        <v>716</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" t="s">
         <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>713</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>717</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="D15">
         <v>30</v>
@@ -3959,13 +3950,13 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>714</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>718</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="D16">
         <v>20</v>
@@ -3976,13 +3967,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>715</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>719</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -3993,13 +3984,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>716</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="B18" t="s">
-        <v>720</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="D18">
         <v>70</v>
@@ -4007,13 +3998,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>717</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B19" t="s">
-        <v>721</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="D19">
         <v>30</v>
@@ -4024,16 +4015,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>718</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B20" t="s">
-        <v>722</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" s="2">
         <v>21</v>
@@ -4041,24 +4032,24 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>719</v>
+      </c>
+      <c r="D21" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>723</v>
-      </c>
-      <c r="D21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
+        <v>720</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>724</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="D22">
         <v>70</v>
@@ -4072,13 +4063,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>721</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="B23" t="s">
-        <v>725</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="D23">
         <v>120</v>
@@ -4089,13 +4080,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>722</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>726</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="D24">
         <v>70</v>
@@ -4103,10 +4094,10 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D29">
         <v>140</v>
@@ -4114,16 +4105,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>724</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
-        <v>728</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30" s="2">
         <v>21</v>
@@ -4131,13 +4122,13 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" t="s">
+        <v>725</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>729</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="D31">
         <v>140</v>
@@ -4145,13 +4136,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>726</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>730</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4162,27 +4153,27 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>727</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B33" t="s">
-        <v>731</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" t="s">
+        <v>728</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="B34" t="s">
-        <v>732</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="D34">
         <v>10</v>
@@ -4196,13 +4187,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>729</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="B35" t="s">
-        <v>733</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D35">
         <v>50</v>
@@ -4213,13 +4204,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" t="s">
+        <v>730</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="B36" t="s">
-        <v>734</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4230,13 +4221,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>731</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="B37" t="s">
-        <v>735</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="D37">
         <v>140</v>
@@ -4244,13 +4235,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" t="s">
+        <v>732</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>736</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="D38">
         <v>60</v>
@@ -4261,13 +4252,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>733</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>737</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="D39">
         <v>110</v>
@@ -4278,13 +4269,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>734</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>738</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="D40">
         <v>100</v>
@@ -4292,27 +4283,27 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>735</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B41" t="s">
-        <v>739</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>736</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B42" t="s">
-        <v>740</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="D42">
         <v>35</v>
@@ -4323,13 +4314,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
+        <v>737</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B43" t="s">
-        <v>741</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -4343,16 +4334,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" t="s">
+        <v>738</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B44" t="s">
-        <v>742</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="D44" t="s">
         <v>84</v>
-      </c>
-      <c r="D44" t="s">
-        <v>85</v>
       </c>
       <c r="E44" s="2">
         <v>11</v>
@@ -4363,10 +4354,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="D45">
         <v>110</v>
@@ -4377,10 +4368,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D46">
         <v>50</v>
@@ -4394,13 +4385,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>741</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="B47" t="s">
-        <v>745</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>89</v>
       </c>
       <c r="D47">
         <v>70</v>
@@ -4408,13 +4399,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>742</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="B48" t="s">
-        <v>746</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="D48">
         <v>90</v>
@@ -4425,13 +4416,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" t="s">
+        <v>743</v>
+      </c>
+      <c r="D49" t="s">
         <v>92</v>
-      </c>
-      <c r="B49" t="s">
-        <v>747</v>
-      </c>
-      <c r="D49" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -4458,7 +4449,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -4486,49 +4477,49 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>96</v>
-      </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>745</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B4" t="s">
-        <v>749</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>98</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>746</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" t="s">
-        <v>750</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -4539,13 +4530,13 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>747</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" t="s">
-        <v>751</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="D6">
         <v>60</v>
@@ -4556,33 +4547,33 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>748</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" t="s">
-        <v>752</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>749</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
         <v>106</v>
-      </c>
-      <c r="B8" t="s">
-        <v>753</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
       </c>
       <c r="E8" s="2">
         <v>21</v>
@@ -4593,13 +4584,13 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
+        <v>750</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>754</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="D9">
         <v>40</v>
@@ -4610,55 +4601,55 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>751</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B10" t="s">
-        <v>755</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>752</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B11" t="s">
-        <v>756</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" t="s">
         <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
+        <v>753</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B12" t="s">
-        <v>757</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>116</v>
-      </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" t="s">
+        <v>754</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="B13" t="s">
-        <v>758</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>118</v>
       </c>
       <c r="D13">
         <v>140</v>
@@ -4666,13 +4657,13 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" t="s">
+        <v>755</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="B14" t="s">
-        <v>759</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="D14">
         <v>75</v>
@@ -4683,13 +4674,13 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15">
         <v>30</v>
@@ -4703,27 +4694,27 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B16" t="s">
-        <v>761</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" t="s">
         <v>123</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" t="s">
+        <v>758</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="B17" t="s">
-        <v>762</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>126</v>
       </c>
       <c r="D17">
         <v>80</v>
@@ -4734,13 +4725,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" t="s">
+        <v>759</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>127</v>
-      </c>
-      <c r="B18" t="s">
-        <v>763</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>128</v>
       </c>
       <c r="D18">
         <v>140</v>
@@ -4748,13 +4739,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>760</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="B19" t="s">
-        <v>764</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>130</v>
       </c>
       <c r="D19">
         <v>70</v>
@@ -4765,10 +4756,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -4779,13 +4770,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>762</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>132</v>
-      </c>
-      <c r="B21" t="s">
-        <v>766</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="D21">
         <v>70</v>
@@ -4793,27 +4784,27 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>763</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B22" t="s">
-        <v>767</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
+        <v>764</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="B23" t="s">
-        <v>768</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>137</v>
       </c>
       <c r="D23">
         <v>140</v>
@@ -4821,13 +4812,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>765</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="B28" t="s">
-        <v>769</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>139</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -4838,30 +4829,30 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" t="s">
+        <v>766</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B29" t="s">
-        <v>770</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" t="s">
+        <v>767</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B30" t="s">
-        <v>771</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" t="s">
         <v>143</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
       </c>
       <c r="E30" s="2">
         <v>70</v>
@@ -4869,13 +4860,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" t="s">
+        <v>768</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="B31" t="s">
-        <v>772</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>146</v>
       </c>
       <c r="D31">
         <v>140</v>
@@ -4883,13 +4874,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
+        <v>769</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="B32" t="s">
-        <v>773</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>148</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4900,13 +4891,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" t="s">
+        <v>770</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="B33" t="s">
-        <v>774</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>150</v>
       </c>
       <c r="D33">
         <v>70</v>
@@ -4914,13 +4905,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" t="s">
+        <v>771</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="B34" t="s">
-        <v>775</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>152</v>
       </c>
       <c r="D34">
         <v>210</v>
@@ -4928,13 +4919,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" t="s">
+        <v>772</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="B35" t="s">
-        <v>776</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>154</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -4942,13 +4933,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" t="s">
+        <v>773</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>155</v>
-      </c>
-      <c r="B36" t="s">
-        <v>777</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="D36">
         <v>50</v>
@@ -4959,13 +4950,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" t="s">
+        <v>774</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="B37" t="s">
-        <v>778</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4979,13 +4970,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38" t="s">
+        <v>775</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>159</v>
-      </c>
-      <c r="B38" t="s">
-        <v>779</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>160</v>
       </c>
       <c r="D38">
         <v>90</v>
@@ -4996,27 +4987,27 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>160</v>
+      </c>
+      <c r="B39" t="s">
+        <v>776</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B39" t="s">
-        <v>780</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" t="s">
+        <v>777</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="B40" t="s">
-        <v>781</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>164</v>
       </c>
       <c r="D40">
         <v>60</v>
@@ -5027,13 +5018,13 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
+        <v>164</v>
+      </c>
+      <c r="B41" t="s">
+        <v>778</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B41" t="s">
-        <v>782</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="D41">
         <v>130</v>
@@ -5041,16 +5032,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" t="s">
+        <v>779</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" t="s">
         <v>167</v>
-      </c>
-      <c r="B42" t="s">
-        <v>783</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" t="s">
-        <v>168</v>
       </c>
       <c r="E42" s="2">
         <v>21</v>
@@ -5058,16 +5049,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" t="s">
+        <v>780</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B43" t="s">
-        <v>784</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>170</v>
-      </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E43" s="2">
         <v>21</v>
@@ -5075,55 +5066,55 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" t="s">
+        <v>781</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B44" t="s">
-        <v>785</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>172</v>
-      </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
+        <v>172</v>
+      </c>
+      <c r="B45" t="s">
+        <v>782</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B45" t="s">
-        <v>786</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>174</v>
-      </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46" t="s">
+        <v>783</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B46" t="s">
-        <v>787</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>176</v>
-      </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
+        <v>176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>784</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="B47" t="s">
-        <v>788</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>178</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -5131,13 +5122,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
+        <v>178</v>
+      </c>
+      <c r="B48" t="s">
+        <v>785</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="B48" t="s">
-        <v>789</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5148,24 +5139,24 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" t="s">
+        <v>786</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B49" t="s">
-        <v>790</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>182</v>
-      </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B50" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -5199,7 +5190,7 @@
     <row r="1" spans="1:6" ht="15" customHeight="1">
       <c r="C1" s="1"/>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5215,64 +5206,64 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
+      <c r="E2" t="s">
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" t="s">
+        <v>788</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B3" t="s">
-        <v>792</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>186</v>
-      </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" t="s">
+        <v>789</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B4" t="s">
-        <v>793</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>188</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" t="s">
+        <v>791</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="B6" t="s">
-        <v>795</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>191</v>
       </c>
       <c r="D6">
         <v>90</v>
@@ -5283,13 +5274,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" t="s">
+        <v>792</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="B7" t="s">
-        <v>796</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="D7">
         <v>140</v>
@@ -5297,27 +5288,27 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B8" t="s">
-        <v>797</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>195</v>
-      </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" t="s">
+        <v>794</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="B9" t="s">
-        <v>798</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="D9">
         <v>140</v>
@@ -5325,13 +5316,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>795</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="B10" t="s">
-        <v>799</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>199</v>
       </c>
       <c r="D10">
         <v>350</v>
@@ -5339,13 +5330,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" t="s">
+        <v>796</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="B11" t="s">
-        <v>800</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>201</v>
       </c>
       <c r="D11">
         <v>280</v>
@@ -5353,13 +5344,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" t="s">
+        <v>797</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="B12" t="s">
-        <v>801</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>203</v>
       </c>
       <c r="D12">
         <v>140</v>
@@ -5367,13 +5358,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" t="s">
+        <v>798</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="B13" t="s">
-        <v>802</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="D13">
         <v>350</v>
@@ -5381,16 +5372,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" t="s">
+        <v>799</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B14" t="s">
-        <v>803</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>207</v>
-      </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E14" s="4">
         <v>63</v>
@@ -5398,27 +5389,27 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" t="s">
+        <v>800</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" t="s">
         <v>208</v>
-      </c>
-      <c r="B15" t="s">
-        <v>804</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" t="s">
+        <v>801</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B16" t="s">
-        <v>805</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>211</v>
       </c>
       <c r="D16">
         <v>170</v>
@@ -5426,27 +5417,27 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" t="s">
+        <v>802</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B17" t="s">
-        <v>806</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>213</v>
-      </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s">
+        <v>803</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B18" t="s">
-        <v>807</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="D18">
         <v>60</v>
@@ -5457,13 +5448,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s">
+        <v>804</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B19" t="s">
-        <v>808</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>217</v>
       </c>
       <c r="D19">
         <v>40</v>
@@ -5474,13 +5465,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" t="s">
+        <v>805</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>809</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>219</v>
       </c>
       <c r="D20">
         <v>140</v>
@@ -5491,16 +5482,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B21" t="s">
+        <v>806</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B21" t="s">
-        <v>810</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" t="s">
         <v>221</v>
-      </c>
-      <c r="D21" t="s">
-        <v>222</v>
       </c>
       <c r="E21" s="4">
         <v>50</v>
@@ -5508,27 +5499,27 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" t="s">
+        <v>807</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B22" t="s">
-        <v>811</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" t="s">
         <v>224</v>
-      </c>
-      <c r="D22" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s">
+        <v>808</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>226</v>
-      </c>
-      <c r="B23" t="s">
-        <v>812</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>227</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -5539,13 +5530,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s">
+        <v>809</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="B24" t="s">
-        <v>813</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>229</v>
       </c>
       <c r="F24" s="2">
         <v>90</v>
@@ -5553,13 +5544,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" t="s">
+        <v>810</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="B27" t="s">
-        <v>814</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>231</v>
       </c>
       <c r="D27">
         <v>214</v>
@@ -5570,13 +5561,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" t="s">
+        <v>811</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="B28" t="s">
-        <v>815</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -5587,13 +5578,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" t="s">
+        <v>812</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="B29" t="s">
-        <v>816</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>235</v>
       </c>
       <c r="D29">
         <v>280</v>
@@ -5601,27 +5592,27 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" t="s">
+        <v>813</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B30" t="s">
-        <v>817</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" t="s">
         <v>237</v>
-      </c>
-      <c r="D30" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B31" t="s">
+        <v>814</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="B31" t="s">
-        <v>818</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>240</v>
       </c>
       <c r="D31">
         <v>170</v>
@@ -5629,13 +5620,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B32" t="s">
+        <v>815</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>241</v>
-      </c>
-      <c r="B32" t="s">
-        <v>819</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>242</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5646,27 +5637,27 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" t="s">
+        <v>816</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B33" t="s">
-        <v>820</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>244</v>
-      </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B34" t="s">
+        <v>817</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="B34" t="s">
-        <v>821</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>246</v>
       </c>
       <c r="D34">
         <v>110</v>
@@ -5677,13 +5668,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B35" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D35">
         <v>240</v>
@@ -5691,27 +5682,27 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B36" t="s">
+        <v>819</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="B36" t="s">
-        <v>823</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>249</v>
-      </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B37" t="s">
+        <v>820</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>250</v>
-      </c>
-      <c r="B37" t="s">
-        <v>824</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="D37">
         <v>280</v>
@@ -5719,13 +5710,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B38" t="s">
+        <v>821</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="B38" t="s">
-        <v>825</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>253</v>
       </c>
       <c r="D38">
         <v>65</v>
@@ -5736,13 +5727,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" t="s">
+        <v>822</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>254</v>
-      </c>
-      <c r="B39" t="s">
-        <v>826</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>255</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5750,41 +5741,41 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B41" t="s">
+        <v>824</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B41" t="s">
-        <v>828</v>
-      </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" t="s">
         <v>258</v>
-      </c>
-      <c r="D41" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" t="s">
+        <v>825</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="B42" t="s">
-        <v>829</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5792,13 +5783,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B43" t="s">
+        <v>826</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="B43" t="s">
-        <v>830</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5806,13 +5797,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B44" t="s">
+        <v>827</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>264</v>
-      </c>
-      <c r="B44" t="s">
-        <v>831</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>265</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5823,41 +5814,41 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B45" t="s">
+        <v>828</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B45" t="s">
-        <v>832</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>267</v>
-      </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B46" t="s">
+        <v>829</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B46" t="s">
-        <v>833</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>269</v>
-      </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" t="s">
+        <v>830</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="B47" t="s">
-        <v>834</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -5887,17 +5878,17 @@
     <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="B1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5910,67 +5901,64 @@
       <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
+      <c r="E2" t="s">
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>274</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
+        <v>831</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>276</v>
       </c>
-      <c r="B3" t="s">
-        <v>835</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B4" t="s">
-        <v>836</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="D4">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B5" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D5">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D6">
         <v>20</v>
@@ -5979,15 +5967,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B7" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5996,15 +5984,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B8" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6013,57 +6001,57 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B9" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D9">
         <v>210</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D10">
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" t="s">
+        <v>839</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>292</v>
       </c>
-      <c r="B11" t="s">
-        <v>843</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B12" t="s">
+        <v>840</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>294</v>
-      </c>
-      <c r="B12" t="s">
-        <v>844</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6072,71 +6060,71 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" t="s">
+        <v>841</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>296</v>
       </c>
-      <c r="B13" t="s">
-        <v>845</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B14" t="s">
+        <v>842</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>298</v>
-      </c>
-      <c r="B14" t="s">
-        <v>846</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>299</v>
       </c>
       <c r="D14">
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B15" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D15">
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B16" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B17" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6147,55 +6135,55 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" t="s">
+        <v>846</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" t="s">
         <v>305</v>
-      </c>
-      <c r="B18" t="s">
-        <v>850</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="D18" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>306</v>
+      </c>
+      <c r="B19" t="s">
+        <v>847</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" t="s">
         <v>308</v>
-      </c>
-      <c r="B19" t="s">
-        <v>851</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="D19" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>309</v>
+      </c>
+      <c r="B20" t="s">
+        <v>848</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D20" t="s">
         <v>311</v>
-      </c>
-      <c r="B20" t="s">
-        <v>852</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D20" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B21" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D21">
         <v>93</v>
@@ -6206,13 +6194,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B22" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6229,13 +6217,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B23" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6246,27 +6234,27 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B24" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B25" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D25">
         <v>350</v>
@@ -6274,13 +6262,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D26">
         <v>210</v>
@@ -6288,13 +6276,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B27" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -6305,13 +6293,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B28" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -6322,13 +6310,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="2">
@@ -6337,10 +6325,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="F30" s="2">
         <v>65</v>
@@ -6348,16 +6336,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" t="s">
+        <v>859</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D32" t="s">
         <v>332</v>
-      </c>
-      <c r="B32" t="s">
-        <v>863</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="D32" t="s">
-        <v>334</v>
       </c>
       <c r="E32" s="4">
         <v>21</v>
@@ -6365,13 +6353,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B33" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D33">
         <v>70</v>
@@ -6379,13 +6367,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D34">
         <v>214</v>
@@ -6396,13 +6384,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D35">
         <v>210</v>
@@ -6410,13 +6398,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D36">
         <v>110</v>
@@ -6424,13 +6412,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D37">
         <v>210</v>
@@ -6438,13 +6426,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D38">
         <v>350</v>
@@ -6452,27 +6440,27 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D40">
         <v>70</v>
@@ -6480,13 +6468,13 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D41">
         <v>80</v>
@@ -6494,13 +6482,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B42" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6511,13 +6499,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D43">
         <v>280</v>
@@ -6525,13 +6513,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D44">
         <v>210</v>
@@ -6539,38 +6527,38 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D46" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D47">
         <v>280</v>
@@ -6578,24 +6566,24 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -6606,13 +6594,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D50">
         <v>160</v>
@@ -6641,7 +6629,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="H1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6658,21 +6646,21 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
-        <v>368</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D3">
         <v>260</v>
@@ -6680,10 +6668,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B4" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D4">
         <v>130</v>
@@ -6694,13 +6682,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B5" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D5">
         <v>120</v>
@@ -6708,24 +6696,24 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B7" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D7">
         <v>148</v>
@@ -6733,10 +6721,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B8" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D8">
         <v>70</v>
@@ -6744,24 +6732,24 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B9" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B10" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -6772,13 +6760,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B11" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D11">
         <v>140</v>
@@ -6786,27 +6774,27 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B12" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B13" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E13" s="2">
         <v>21</v>
@@ -6814,35 +6802,35 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D14" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B15" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D16">
         <v>210</v>
@@ -6850,27 +6838,27 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B17" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B18" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D18">
         <v>160</v>
@@ -6878,13 +6866,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B19" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D19">
         <v>340</v>
@@ -6892,35 +6880,35 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B20" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D20" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B21" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D21" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B22" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D22">
         <v>373</v>
@@ -6928,13 +6916,13 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B23" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D23">
         <v>145</v>
@@ -6945,10 +6933,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B24" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D24">
         <v>150</v>
@@ -6956,13 +6944,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B25" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D25">
         <v>250</v>
@@ -6970,13 +6958,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B26" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D26">
         <v>70</v>
@@ -6987,27 +6975,27 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B27" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B28" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D28">
         <v>420</v>
@@ -7015,13 +7003,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B29" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D29">
         <v>140</v>
@@ -7029,30 +7017,30 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B30" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B34" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D34">
         <v>140</v>
@@ -7060,13 +7048,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B35" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35">
         <v>50</v>
@@ -7077,13 +7065,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B36" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D36">
         <v>552</v>
@@ -7094,13 +7082,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B37" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7114,13 +7102,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B38" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D38">
         <v>210</v>
@@ -7128,13 +7116,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B39" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D39">
         <v>50</v>
@@ -7145,13 +7133,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B40" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D40">
         <v>175</v>
@@ -7159,27 +7147,27 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B41" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B42" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D42">
         <v>210</v>
@@ -7187,13 +7175,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B43" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D43">
         <v>100</v>
@@ -7204,27 +7192,27 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D45">
         <v>380</v>
@@ -7232,27 +7220,27 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D46" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D47">
         <v>214</v>
@@ -7263,10 +7251,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D48">
         <v>490</v>
@@ -7274,13 +7262,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D49">
         <v>490</v>
@@ -7288,10 +7276,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D50">
         <v>34</v>
@@ -7302,38 +7290,38 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D52" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D53">
         <v>140</v>
@@ -7341,13 +7329,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D54">
         <v>10</v>
@@ -7358,7 +7346,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -7383,7 +7371,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="H1" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7400,27 +7388,24 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>1028</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>455</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B3" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E3" s="2">
         <v>21</v>
@@ -7431,13 +7416,13 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B4" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -7448,13 +7433,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B5" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -7465,13 +7450,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -7482,13 +7467,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B7" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -7502,30 +7487,30 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B8" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D8">
         <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B9" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D9">
         <v>22</v>
@@ -7536,10 +7521,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B10" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="D10">
         <v>230</v>
@@ -7550,13 +7535,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B11" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>170</v>
@@ -7564,10 +7549,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B12" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D12">
         <v>190</v>
@@ -7575,16 +7560,16 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B13" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2">
         <v>21</v>
@@ -7592,10 +7577,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B14" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D14">
         <v>140</v>
@@ -7603,10 +7588,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B15" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="D15">
         <v>250</v>
@@ -7614,27 +7599,27 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B16" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B17" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -7645,52 +7630,52 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B18" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D18" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B19" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B20" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B21" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D21">
         <v>210</v>
@@ -7701,13 +7686,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B22" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7718,16 +7703,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B23" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D23" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E23" s="2">
         <v>21</v>
@@ -7738,13 +7723,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B24" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D24">
         <v>280</v>
@@ -7752,13 +7737,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B25" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7769,13 +7754,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B26" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D26">
         <v>140</v>
@@ -7783,27 +7768,27 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B31" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B32" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7817,16 +7802,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B33" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D33" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E33">
         <v>-9</v>
@@ -7834,13 +7819,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B34" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7854,10 +7839,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B35" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D35">
         <v>60</v>
@@ -7868,10 +7853,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B36" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7885,13 +7870,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B37" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7902,10 +7887,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B38" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D38">
         <v>150</v>
@@ -7916,13 +7901,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B39" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D39">
         <v>270</v>
@@ -7930,24 +7915,24 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B40" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B41" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -7961,24 +7946,24 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B42" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D42" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B43" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D43">
         <v>45</v>
@@ -7989,13 +7974,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B44" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D44">
         <v>350</v>
@@ -8003,10 +7988,10 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B45" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D45">
         <v>210</v>
@@ -8017,13 +8002,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B46" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -8034,13 +8019,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B47" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -8051,13 +8036,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B48" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -8068,13 +8053,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B49" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D49">
         <v>70</v>
@@ -8082,13 +8067,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B50" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -8102,13 +8087,13 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B51" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D51">
         <v>70</v>
@@ -8116,16 +8101,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B52" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="D52" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E52" s="2">
         <v>47</v>
@@ -8133,13 +8118,13 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B53" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -8169,7 +8154,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="C1" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8191,13 +8176,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B3" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D3">
         <v>350</v>
@@ -8205,52 +8190,52 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B4" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B5" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B6" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B7" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="D7">
         <v>164</v>
@@ -8258,55 +8243,55 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B8" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B9" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B10" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B11" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="D11">
         <v>210</v>
@@ -8314,13 +8299,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B12" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8331,13 +8316,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B13" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D13">
         <v>90</v>
@@ -8348,13 +8333,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B14" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -8365,13 +8350,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B20" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D20">
         <v>210</v>
@@ -8379,13 +8364,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B21" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="D21">
         <v>270</v>
@@ -8393,13 +8378,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B22" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="D22">
         <v>350</v>
@@ -8407,41 +8392,41 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B23" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B24" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B25" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D25">
         <v>140</v>
@@ -8452,13 +8437,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B26" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8469,13 +8454,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B27" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D27">
         <v>420</v>
@@ -8483,13 +8468,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B28" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D28">
         <v>490</v>
@@ -8497,13 +8482,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B29" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D29">
         <v>70</v>
@@ -8514,66 +8499,66 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B30" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B31" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D31" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B32" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B33" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D33" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B34" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8584,27 +8569,27 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B35" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B36" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -8612,13 +8597,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B37" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="D37">
         <v>140</v>
@@ -8626,27 +8611,27 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B38" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B39" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D39">
         <v>420</v>
@@ -8654,13 +8639,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B40" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D40">
         <v>110</v>
@@ -8668,10 +8653,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B41" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="D41">
         <v>180</v>
@@ -8679,13 +8664,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B42" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D42">
         <v>420</v>
@@ -8693,13 +8678,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B43" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="D43">
         <v>70</v>
@@ -8707,13 +8692,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B44" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D44">
         <v>280</v>
@@ -8721,13 +8706,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B45" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D45">
         <v>210</v>
@@ -8754,7 +8739,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="F1" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8771,32 +8756,32 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B3" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="D3" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B4" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D4">
         <v>70</v>
@@ -8807,69 +8792,69 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B5" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D5" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B6" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B7" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B8" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B9" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D9">
         <v>200</v>
@@ -8877,13 +8862,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B10" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D10">
         <v>70</v>
@@ -8891,13 +8876,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B11" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D11">
         <v>30</v>
@@ -8908,10 +8893,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B12" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -8922,27 +8907,27 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B13" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D13" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B14" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D14">
         <v>40</v>
@@ -8953,27 +8938,27 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B15" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B16" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -8984,16 +8969,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B17" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" s="2">
         <v>21</v>
@@ -9001,58 +8986,58 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B18" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B19" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D19" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B20" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B21" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D21" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E21" s="2">
         <v>10</v>
@@ -9060,27 +9045,27 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B22" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D22" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B23" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -9091,13 +9076,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B24" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D24">
         <v>230</v>
@@ -9105,13 +9090,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B28" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D28">
         <v>90</v>
@@ -9119,16 +9104,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B29" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2">
         <v>21</v>
@@ -9136,13 +9121,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B30" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D30">
         <v>410</v>
@@ -9153,27 +9138,27 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B31" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B32" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -9181,13 +9166,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B33" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="D33">
         <v>140</v>
@@ -9195,13 +9180,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B34" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D34">
         <v>210</v>
@@ -9212,13 +9197,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B35" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -9229,13 +9214,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B36" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -9246,27 +9231,27 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B37" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D37" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B38" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D38">
         <v>70</v>
@@ -9274,13 +9259,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B39" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D39">
         <v>350</v>
@@ -9288,13 +9273,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B40" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D40">
         <v>210</v>
@@ -9302,13 +9287,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B41" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D41">
         <v>138</v>
@@ -9316,13 +9301,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B42" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D42">
         <v>210</v>
@@ -9330,10 +9315,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B43" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D43">
         <v>210</v>
@@ -9341,16 +9326,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B44" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E44" s="2">
         <v>21</v>
